--- a/blanketter/blankett_forvaltarkunskap_nnk.xlsx
+++ b/blanketter/blankett_forvaltarkunskap_nnk.xlsx
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,6 +206,7 @@
     </xf>
     <xf numFmtId="1" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -740,7 +741,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.4, 2026-08-26</t>
+          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.5, 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -856,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="98" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
           <t>8.</t>
@@ -864,7 +865,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Kolumn I, "Förvaltare", är nytt sedan version 1.3 — kopplat automatiskt utifrån länsstyrelsens förvaltarlista (uttag 2026-05-27, 576 av 628 rader har en träff). "(?)" efter namnet betyder osäker namn-matchning, kontrollera innan du litar på den. Tomt fält betyder att området inte gick att koppla automatiskt — se data/forvaltare/README.md for de 10 objekt som kräver manuell koppling. Detta täcker i stort uppgift H1.1 i arbetsplanen.</t>
+          <t>Kolumn I, "Förvaltare", är nytt sedan version 1.3 — kopplat automatiskt utifrån länsstyrelsens förvaltarlista (uttag 2026-05-27, 576 av 628 rader har en träff). "(?)" efter namnet betyder osäker namn-matchning, kontrollera innan du litar på den. Tomt fält betyder att området inte gick att koppla automatiskt — se data/forvaltare/README.md for de 10 objekt som kräver manuell koppling. Detta täcker i stort uppgift H1.1 i arbetsplanen. Sedan version 1.5 visas fullt namn i stället för bara förnamn, med en klickbar mailto-länk till LST-personens e-post — enligt handläggarlistan i data/forvaltare/handlaggare_lst.csv, inte hämtat automatiskt ur något system.</t>
         </is>
       </c>
     </row>
@@ -4151,9 +4152,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
@@ -4220,9 +4221,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -4289,9 +4290,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
@@ -4358,9 +4359,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
@@ -4427,9 +4428,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
@@ -4496,9 +4497,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
@@ -4565,9 +4566,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
@@ -4634,9 +4635,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
@@ -4703,9 +4704,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J56" s="12" t="inlineStr">
@@ -4772,9 +4773,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
@@ -4841,9 +4842,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J58" s="12" t="inlineStr">
@@ -4910,9 +4911,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
@@ -4979,9 +4980,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J60" s="13" t="inlineStr">
@@ -5048,9 +5049,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J61" s="13" t="inlineStr">
@@ -6287,9 +6288,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J80" s="13" t="inlineStr">
@@ -6352,9 +6353,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J81" s="13" t="inlineStr">
@@ -6417,9 +6418,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J82" s="13" t="inlineStr">
@@ -6482,9 +6483,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J83" s="13" t="inlineStr">
@@ -6547,9 +6548,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J84" s="13" t="inlineStr">
@@ -6612,9 +6613,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J85" s="13" t="inlineStr">
@@ -6677,9 +6678,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J86" s="13" t="inlineStr">
@@ -6742,9 +6743,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J87" s="13" t="inlineStr">
@@ -7587,9 +7588,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J100" s="12" t="inlineStr">
@@ -7652,9 +7653,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J101" s="12" t="inlineStr">
@@ -7717,9 +7718,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J102" s="12" t="inlineStr">
@@ -7782,9 +7783,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J103" s="12" t="inlineStr">
@@ -7851,9 +7852,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J104" s="12" t="inlineStr">
@@ -7920,9 +7921,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J105" s="12" t="inlineStr">
@@ -7989,9 +7990,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
@@ -8058,9 +8059,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I107" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -8127,9 +8128,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J108" s="13" t="inlineStr">
@@ -8196,9 +8197,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I109" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
@@ -8265,9 +8266,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
@@ -8334,9 +8335,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -8403,9 +8404,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
@@ -8472,9 +8473,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -8541,9 +8542,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I114" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
@@ -8610,9 +8611,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -8679,9 +8680,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J116" s="13" t="inlineStr">
@@ -8748,9 +8749,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J117" s="12" t="inlineStr">
@@ -8817,9 +8818,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J118" s="12" t="inlineStr">
@@ -8886,9 +8887,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I119" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J119" s="12" t="inlineStr">
@@ -8955,9 +8956,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I120" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J120" s="12" t="inlineStr">
@@ -9024,9 +9025,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I121" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J121" s="13" t="inlineStr">
@@ -9093,9 +9094,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I122" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J122" s="12" t="inlineStr">
@@ -9158,9 +9159,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J123" s="12" t="inlineStr">
@@ -9223,9 +9224,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I124" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J124" s="12" t="inlineStr">
@@ -9288,9 +9289,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I125" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J125" s="12" t="inlineStr">
@@ -9353,9 +9354,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J126" s="13" t="inlineStr">
@@ -9418,9 +9419,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J127" s="12" t="inlineStr">
@@ -9483,9 +9484,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I128" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J128" s="12" t="inlineStr">
@@ -9552,9 +9553,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I129" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J129" s="12" t="inlineStr">
@@ -9621,9 +9622,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I130" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J130" s="12" t="inlineStr">
@@ -9690,9 +9691,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I131" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J131" s="12" t="inlineStr">
@@ -9759,9 +9760,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J132" s="12" t="inlineStr">
@@ -9828,9 +9829,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J133" s="12" t="inlineStr">
@@ -9897,9 +9898,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J134" s="13" t="inlineStr">
@@ -9966,9 +9967,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I135" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J135" s="13" t="inlineStr">
@@ -10035,9 +10036,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>Robin</t>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>Robin Pettersson</t>
         </is>
       </c>
       <c r="J136" s="13" t="inlineStr">
@@ -10104,9 +10105,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I137" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J137" s="13" t="inlineStr">
@@ -10169,9 +10170,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J138" s="13" t="inlineStr">
@@ -10234,9 +10235,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I139" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J139" s="13" t="inlineStr">
@@ -10299,9 +10300,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J140" s="13" t="inlineStr">
@@ -10916,9 +10917,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I149" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
@@ -10981,9 +10982,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I150" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J150" s="12" t="inlineStr">
@@ -11046,9 +11047,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
@@ -11111,9 +11112,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I152" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J152" s="12" t="inlineStr">
@@ -11176,9 +11177,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
@@ -11241,9 +11242,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I154" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J154" s="13" t="inlineStr">
@@ -11631,9 +11632,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I160" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I160" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J160" s="12" t="inlineStr">
@@ -11700,9 +11701,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I161" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J161" s="12" t="inlineStr">
@@ -11769,9 +11770,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I162" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J162" s="12" t="inlineStr">
@@ -11838,9 +11839,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J163" s="12" t="inlineStr">
@@ -11907,9 +11908,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I164" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J164" s="12" t="inlineStr">
@@ -11976,9 +11977,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I165" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J165" s="12" t="inlineStr">
@@ -12045,9 +12046,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I166" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J166" s="12" t="inlineStr">
@@ -12114,9 +12115,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J167" s="12" t="inlineStr">
@@ -12179,9 +12180,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I168" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J168" s="12" t="inlineStr">
@@ -12244,9 +12245,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I169" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J169" s="12" t="inlineStr">
@@ -12309,9 +12310,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I170" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J170" s="12" t="inlineStr">
@@ -12374,9 +12375,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I171" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J171" s="12" t="inlineStr">
@@ -12439,9 +12440,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I172" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J172" s="12" t="inlineStr">
@@ -12504,9 +12505,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I173" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J173" s="13" t="inlineStr">
@@ -12569,9 +12570,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I174" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J174" s="12" t="inlineStr">
@@ -12634,9 +12635,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I175" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -12699,9 +12700,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I176" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
@@ -12764,9 +12765,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I177" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
@@ -12829,9 +12830,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I178" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J178" s="12" t="inlineStr">
@@ -12959,9 +12960,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I180" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J180" s="12" t="inlineStr">
@@ -13024,9 +13025,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I181" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J181" s="12" t="inlineStr">
@@ -13089,9 +13090,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I182" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J182" s="13" t="inlineStr">
@@ -13154,9 +13155,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I183" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J183" s="12" t="inlineStr">
@@ -13219,9 +13220,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I184" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I184" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J184" s="12" t="inlineStr">
@@ -13288,9 +13289,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I185" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I185" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J185" s="12" t="inlineStr">
@@ -13357,9 +13358,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I186" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J186" s="12" t="inlineStr">
@@ -13426,9 +13427,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I187" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I187" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J187" s="12" t="inlineStr">
@@ -13495,9 +13496,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I188" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J188" s="12" t="inlineStr">
@@ -13564,9 +13565,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I189" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J189" s="12" t="inlineStr">
@@ -13629,9 +13630,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I190" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I190" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J190" s="12" t="inlineStr">
@@ -13694,9 +13695,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I191" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J191" s="12" t="inlineStr">
@@ -13759,9 +13760,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I192" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J192" s="12" t="inlineStr">
@@ -13824,9 +13825,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I193" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J193" s="12" t="inlineStr">
@@ -13889,9 +13890,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I194" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J194" s="12" t="inlineStr">
@@ -13954,9 +13955,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I195" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J195" s="12" t="inlineStr">
@@ -14019,9 +14020,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I196" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I196" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J196" s="12" t="inlineStr">
@@ -14084,9 +14085,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I197" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I197" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J197" s="12" t="inlineStr">
@@ -14149,9 +14150,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I198" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J198" s="12" t="inlineStr">
@@ -14214,9 +14215,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I199" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J199" s="12" t="inlineStr">
@@ -14283,9 +14284,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I200" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I200" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J200" s="12" t="inlineStr">
@@ -14352,9 +14353,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I201" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J201" s="12" t="inlineStr">
@@ -14421,9 +14422,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I202" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I202" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J202" s="12" t="inlineStr">
@@ -14490,9 +14491,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I203" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I203" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J203" s="13" t="inlineStr">
@@ -15014,9 +15015,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I211" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I211" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J211" s="12" t="inlineStr">
@@ -15079,9 +15080,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I212" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I212" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J212" s="12" t="inlineStr">
@@ -15144,9 +15145,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I213" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I213" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J213" s="12" t="inlineStr">
@@ -15209,9 +15210,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I214" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I214" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J214" s="12" t="inlineStr">
@@ -15274,9 +15275,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I215" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I215" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J215" s="12" t="inlineStr">
@@ -15339,9 +15340,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I216" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I216" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J216" s="12" t="inlineStr">
@@ -15404,9 +15405,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I217" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I217" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J217" s="12" t="inlineStr">
@@ -15469,9 +15470,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I218" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I218" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J218" s="12" t="inlineStr">
@@ -15534,9 +15535,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I219" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I219" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J219" s="12" t="inlineStr">
@@ -15599,9 +15600,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I220" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I220" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J220" s="12" t="inlineStr">
@@ -15664,9 +15665,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I221" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I221" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J221" s="13" t="inlineStr">
@@ -15729,9 +15730,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I222" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I222" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J222" s="12" t="inlineStr">
@@ -15794,9 +15795,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I223" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I223" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J223" s="12" t="inlineStr">
@@ -15859,9 +15860,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I224" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I224" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J224" s="12" t="inlineStr">
@@ -15924,9 +15925,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I225" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I225" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J225" s="12" t="inlineStr">
@@ -15989,9 +15990,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I226" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I226" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J226" s="12" t="inlineStr">
@@ -16054,9 +16055,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I227" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I227" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J227" s="12" t="inlineStr">
@@ -16123,9 +16124,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I228" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I228" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J228" s="12" t="inlineStr">
@@ -16192,9 +16193,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I229" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I229" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J229" s="12" t="inlineStr">
@@ -16257,9 +16258,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I230" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I230" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J230" s="12" t="inlineStr">
@@ -16322,9 +16323,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I231" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I231" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J231" s="12" t="inlineStr">
@@ -16387,9 +16388,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I232" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I232" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J232" s="12" t="inlineStr">
@@ -16452,9 +16453,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I233" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I233" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J233" s="12" t="inlineStr">
@@ -16517,9 +16518,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I234" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I234" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J234" s="12" t="inlineStr">
@@ -16582,9 +16583,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I235" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I235" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J235" s="13" t="inlineStr">
@@ -16647,9 +16648,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I236" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I236" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J236" s="13" t="inlineStr">
@@ -16712,9 +16713,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I237" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I237" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J237" s="13" t="inlineStr">
@@ -16777,9 +16778,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I238" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I238" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J238" s="13" t="inlineStr">
@@ -16842,9 +16843,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I239" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I239" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J239" s="13" t="inlineStr">
@@ -16907,9 +16908,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I240" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I240" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J240" s="12" t="inlineStr">
@@ -16972,9 +16973,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I241" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I241" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J241" s="13" t="inlineStr">
@@ -17037,9 +17038,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I242" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I242" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J242" s="12" t="inlineStr">
@@ -17102,9 +17103,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I243" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I243" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J243" s="12" t="inlineStr">
@@ -17167,9 +17168,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I244" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I244" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J244" s="12" t="inlineStr">
@@ -17236,9 +17237,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I245" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I245" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J245" s="12" t="inlineStr">
@@ -17305,9 +17306,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I246" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I246" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J246" s="12" t="inlineStr">
@@ -17374,9 +17375,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I247" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I247" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J247" s="12" t="inlineStr">
@@ -17809,9 +17810,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I254" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I254" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J254" s="13" t="inlineStr">
@@ -17874,9 +17875,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I255" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I255" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J255" s="12" t="inlineStr">
@@ -17939,9 +17940,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I256" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I256" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J256" s="12" t="inlineStr">
@@ -18004,9 +18005,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I257" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I257" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J257" s="12" t="inlineStr">
@@ -18069,9 +18070,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I258" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I258" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J258" s="12" t="inlineStr">
@@ -18134,9 +18135,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I259" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I259" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
@@ -18199,9 +18200,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I260" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I260" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J260" s="13" t="inlineStr">
@@ -18264,9 +18265,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I261" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I261" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
@@ -18329,9 +18330,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I262" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I262" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J262" s="12" t="inlineStr">
@@ -18394,9 +18395,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I263" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I263" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
@@ -18459,9 +18460,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I264" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I264" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J264" s="13" t="inlineStr">
@@ -18524,9 +18525,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I265" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I265" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J265" s="13" t="inlineStr">
@@ -18593,9 +18594,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I266" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I266" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J266" s="12" t="inlineStr">
@@ -18662,9 +18663,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I267" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I267" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J267" s="13" t="inlineStr">
@@ -18731,9 +18732,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I268" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I268" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J268" s="12" t="inlineStr">
@@ -18800,9 +18801,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I269" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I269" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J269" s="13" t="inlineStr">
@@ -18869,9 +18870,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I270" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I270" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J270" s="13" t="inlineStr">
@@ -18938,9 +18939,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I271" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I271" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J271" s="12" t="inlineStr">
@@ -19003,9 +19004,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I272" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I272" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J272" s="13" t="inlineStr">
@@ -19068,9 +19069,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I273" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I273" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J273" s="12" t="inlineStr">
@@ -19137,9 +19138,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I274" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I274" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J274" s="12" t="inlineStr">
@@ -19206,9 +19207,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I275" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I275" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J275" s="13" t="inlineStr">
@@ -19275,9 +19276,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I276" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I276" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J276" s="12" t="inlineStr">
@@ -19344,9 +19345,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I277" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I277" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J277" s="12" t="inlineStr">
@@ -19413,9 +19414,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I278" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I278" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J278" s="12" t="inlineStr">
@@ -19482,9 +19483,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I279" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I279" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J279" s="12" t="inlineStr">
@@ -19551,9 +19552,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I280" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I280" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J280" s="12" t="inlineStr">
@@ -19620,9 +19621,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I281" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I281" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J281" s="12" t="inlineStr">
@@ -19685,9 +19686,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I282" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I282" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J282" s="12" t="inlineStr">
@@ -19750,9 +19751,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I283" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I283" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -19815,9 +19816,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I284" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I284" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
@@ -19880,9 +19881,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I285" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I285" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J285" s="12" t="inlineStr">
@@ -20725,9 +20726,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I298" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I298" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J298" s="12" t="inlineStr">
@@ -20790,9 +20791,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I299" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I299" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J299" s="12" t="inlineStr">
@@ -20855,9 +20856,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I300" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I300" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J300" s="13" t="inlineStr">
@@ -20920,9 +20921,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I301" s="10" t="inlineStr">
-        <is>
-          <t>Martin (?)</t>
+      <c r="I301" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist (?)</t>
         </is>
       </c>
       <c r="J301" s="12" t="inlineStr">
@@ -20985,9 +20986,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I302" s="10" t="inlineStr">
-        <is>
-          <t>Martin (?)</t>
+      <c r="I302" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist (?)</t>
         </is>
       </c>
       <c r="J302" s="12" t="inlineStr">
@@ -21180,9 +21181,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I305" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I305" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J305" s="12" t="inlineStr">
@@ -21249,9 +21250,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I306" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I306" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J306" s="12" t="inlineStr">
@@ -21318,9 +21319,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I307" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I307" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J307" s="12" t="inlineStr">
@@ -21387,9 +21388,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I308" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I308" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J308" s="12" t="inlineStr">
@@ -21456,9 +21457,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I309" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I309" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J309" s="12" t="inlineStr">
@@ -21525,9 +21526,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I310" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I310" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J310" s="12" t="inlineStr">
@@ -21590,9 +21591,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I311" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I311" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J311" s="12" t="inlineStr">
@@ -21655,9 +21656,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I312" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I312" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J312" s="12" t="inlineStr">
@@ -21720,9 +21721,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I313" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I313" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J313" s="12" t="inlineStr">
@@ -21785,9 +21786,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I314" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I314" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J314" s="12" t="inlineStr">
@@ -21850,9 +21851,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I315" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I315" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J315" s="12" t="inlineStr">
@@ -21915,9 +21916,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I316" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I316" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J316" s="12" t="inlineStr">
@@ -21980,9 +21981,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I317" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I317" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J317" s="12" t="inlineStr">
@@ -22049,9 +22050,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I318" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I318" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J318" s="13" t="inlineStr">
@@ -22118,9 +22119,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I319" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I319" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J319" s="12" t="inlineStr">
@@ -22577,9 +22578,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I326" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I326" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J326" s="12" t="inlineStr">
@@ -22642,9 +22643,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I327" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I327" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J327" s="12" t="inlineStr">
@@ -22707,9 +22708,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I328" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I328" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J328" s="13" t="inlineStr">
@@ -22772,9 +22773,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I329" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I329" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J329" s="12" t="inlineStr">
@@ -22837,9 +22838,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I330" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I330" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J330" s="13" t="inlineStr">
@@ -22902,9 +22903,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I331" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I331" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J331" s="12" t="inlineStr">
@@ -22967,9 +22968,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I332" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I332" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J332" s="13" t="inlineStr">
@@ -23032,9 +23033,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I333" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I333" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J333" s="12" t="inlineStr">
@@ -23097,9 +23098,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I334" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I334" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J334" s="12" t="inlineStr">
@@ -23166,9 +23167,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I335" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I335" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J335" s="13" t="inlineStr">
@@ -23235,9 +23236,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I336" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I336" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J336" s="12" t="inlineStr">
@@ -23300,9 +23301,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I337" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I337" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J337" s="13" t="inlineStr">
@@ -23365,9 +23366,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I338" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I338" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J338" s="12" t="inlineStr">
@@ -23430,9 +23431,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I339" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I339" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J339" s="12" t="inlineStr">
@@ -23495,9 +23496,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I340" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I340" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J340" s="12" t="inlineStr">
@@ -23564,9 +23565,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I341" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I341" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J341" s="13" t="inlineStr">
@@ -23633,9 +23634,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I342" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I342" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J342" s="12" t="inlineStr">
@@ -23702,9 +23703,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I343" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I343" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J343" s="12" t="inlineStr">
@@ -23767,9 +23768,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I344" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I344" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J344" s="12" t="inlineStr">
@@ -23832,9 +23833,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I345" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I345" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J345" s="13" t="inlineStr">
@@ -23897,9 +23898,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I346" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I346" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J346" s="12" t="inlineStr">
@@ -23962,9 +23963,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I347" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I347" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J347" s="12" t="inlineStr">
@@ -24027,9 +24028,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I348" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I348" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
@@ -24092,9 +24093,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I349" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I349" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J349" s="12" t="inlineStr">
@@ -24157,9 +24158,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I350" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I350" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J350" s="12" t="inlineStr">
@@ -24222,9 +24223,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I351" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I351" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J351" s="12" t="inlineStr">
@@ -24470,9 +24471,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I355" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I355" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J355" s="12" t="inlineStr">
@@ -24539,9 +24540,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I356" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I356" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J356" s="12" t="inlineStr">
@@ -24604,9 +24605,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I357" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I357" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J357" s="12" t="inlineStr">
@@ -24669,9 +24670,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I358" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I358" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J358" s="13" t="inlineStr">
@@ -24734,9 +24735,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I359" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I359" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J359" s="12" t="inlineStr">
@@ -24799,9 +24800,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I360" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I360" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J360" s="12" t="inlineStr">
@@ -24864,9 +24865,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I361" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I361" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J361" s="13" t="inlineStr">
@@ -24929,9 +24930,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I362" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I362" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J362" s="12" t="inlineStr">
@@ -24994,9 +24995,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I363" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I363" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J363" s="12" t="inlineStr">
@@ -25059,9 +25060,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I364" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I364" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J364" s="13" t="inlineStr">
@@ -25124,9 +25125,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I365" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I365" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J365" s="12" t="inlineStr">
@@ -25189,9 +25190,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I366" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I366" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J366" s="12" t="inlineStr">
@@ -25254,9 +25255,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I367" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I367" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J367" s="13" t="inlineStr">
@@ -25319,9 +25320,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I368" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I368" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J368" s="12" t="inlineStr">
@@ -25384,9 +25385,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I369" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I369" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J369" s="12" t="inlineStr">
@@ -25449,9 +25450,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I370" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I370" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J370" s="12" t="inlineStr">
@@ -25697,9 +25698,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I374" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I374" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J374" s="12" t="inlineStr">
@@ -25762,9 +25763,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I375" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I375" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J375" s="12" t="inlineStr">
@@ -25831,9 +25832,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I376" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I376" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J376" s="12" t="inlineStr">
@@ -25900,9 +25901,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I377" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I377" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J377" s="12" t="inlineStr">
@@ -25965,9 +25966,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I378" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I378" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J378" s="12" t="inlineStr">
@@ -26030,9 +26031,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I379" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I379" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J379" s="12" t="inlineStr">
@@ -26095,9 +26096,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I380" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I380" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J380" s="12" t="inlineStr">
@@ -26160,9 +26161,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I381" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I381" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J381" s="12" t="inlineStr">
@@ -26229,9 +26230,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I382" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I382" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J382" s="12" t="inlineStr">
@@ -26298,9 +26299,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I383" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I383" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J383" s="13" t="inlineStr">
@@ -26367,9 +26368,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I384" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I384" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J384" s="12" t="inlineStr">
@@ -26436,9 +26437,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I385" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I385" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J385" s="12" t="inlineStr">
@@ -26501,9 +26502,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I386" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I386" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J386" s="12" t="inlineStr">
@@ -26566,9 +26567,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I387" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I387" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J387" s="13" t="inlineStr">
@@ -26631,9 +26632,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I388" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I388" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J388" s="12" t="inlineStr">
@@ -26700,9 +26701,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I389" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I389" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J389" s="12" t="inlineStr">
@@ -26769,9 +26770,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I390" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I390" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J390" s="12" t="inlineStr">
@@ -26838,9 +26839,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I391" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I391" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J391" s="12" t="inlineStr">
@@ -26903,9 +26904,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I392" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I392" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J392" s="13" t="inlineStr">
@@ -26968,9 +26969,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I393" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I393" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J393" s="12" t="inlineStr">
@@ -27037,9 +27038,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I394" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I394" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J394" s="12" t="inlineStr">
@@ -27106,9 +27107,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I395" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I395" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J395" s="12" t="inlineStr">
@@ -27175,9 +27176,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I396" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I396" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J396" s="12" t="inlineStr">
@@ -27244,9 +27245,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I397" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I397" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J397" s="12" t="inlineStr">
@@ -27313,9 +27314,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I398" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I398" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J398" s="12" t="inlineStr">
@@ -27382,9 +27383,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I399" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I399" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J399" s="12" t="inlineStr">
@@ -27451,9 +27452,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I400" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I400" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J400" s="12" t="inlineStr">
@@ -27520,9 +27521,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I401" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I401" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J401" s="12" t="inlineStr">
@@ -27585,9 +27586,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I402" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I402" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J402" s="12" t="inlineStr">
@@ -27650,9 +27651,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I403" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I403" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J403" s="12" t="inlineStr">
@@ -27715,9 +27716,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I404" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I404" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J404" s="12" t="inlineStr">
@@ -27780,9 +27781,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I405" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I405" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J405" s="12" t="inlineStr">
@@ -27845,9 +27846,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I406" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I406" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J406" s="12" t="inlineStr">
@@ -27910,9 +27911,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I407" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I407" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J407" s="12" t="inlineStr">
@@ -27975,9 +27976,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I408" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I408" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J408" s="12" t="inlineStr">
@@ -28040,9 +28041,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I409" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I409" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J409" s="12" t="inlineStr">
@@ -28105,9 +28106,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I410" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I410" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J410" s="12" t="inlineStr">
@@ -28170,9 +28171,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I411" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I411" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J411" s="13" t="inlineStr">
@@ -28235,9 +28236,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I412" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I412" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J412" s="12" t="inlineStr">
@@ -28300,9 +28301,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I413" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I413" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J413" s="12" t="inlineStr">
@@ -28365,9 +28366,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I414" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I414" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J414" s="12" t="inlineStr">
@@ -28430,9 +28431,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I415" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I415" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J415" s="12" t="inlineStr">
@@ -28495,9 +28496,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I416" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I416" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J416" s="12" t="inlineStr">
@@ -28560,9 +28561,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I417" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I417" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J417" s="12" t="inlineStr">
@@ -28625,9 +28626,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I418" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I418" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J418" s="12" t="inlineStr">
@@ -28690,9 +28691,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I419" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I419" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J419" s="12" t="inlineStr">
@@ -28755,9 +28756,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I420" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I420" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J420" s="12" t="inlineStr">
@@ -28820,9 +28821,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I421" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I421" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J421" s="12" t="inlineStr">
@@ -28885,9 +28886,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I422" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I422" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J422" s="12" t="inlineStr">
@@ -28950,9 +28951,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I423" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I423" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J423" s="12" t="inlineStr">
@@ -29019,9 +29020,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I424" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I424" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J424" s="12" t="inlineStr">
@@ -29088,9 +29089,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I425" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I425" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J425" s="12" t="inlineStr">
@@ -29153,9 +29154,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I426" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I426" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J426" s="12" t="inlineStr">
@@ -29218,9 +29219,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I427" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I427" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J427" s="12" t="inlineStr">
@@ -29283,9 +29284,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I428" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I428" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J428" s="12" t="inlineStr">
@@ -29348,9 +29349,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I429" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I429" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J429" s="13" t="inlineStr">
@@ -29413,9 +29414,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I430" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I430" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J430" s="13" t="inlineStr">
@@ -29478,9 +29479,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I431" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I431" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J431" s="12" t="inlineStr">
@@ -29543,9 +29544,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I432" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I432" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J432" s="12" t="inlineStr">
@@ -29608,9 +29609,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I433" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I433" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J433" s="12" t="inlineStr">
@@ -29673,9 +29674,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I434" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I434" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J434" s="12" t="inlineStr">
@@ -29738,9 +29739,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I435" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I435" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J435" s="12" t="inlineStr">
@@ -29803,9 +29804,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I436" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I436" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J436" s="12" t="inlineStr">
@@ -29872,9 +29873,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I437" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I437" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J437" s="12" t="inlineStr">
@@ -29941,9 +29942,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I438" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I438" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J438" s="12" t="inlineStr">
@@ -30010,9 +30011,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I439" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I439" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J439" s="13" t="inlineStr">
@@ -30075,9 +30076,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I440" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I440" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J440" s="13" t="inlineStr">
@@ -30140,9 +30141,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I441" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I441" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J441" s="13" t="inlineStr">
@@ -30205,9 +30206,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I442" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I442" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J442" s="12" t="inlineStr">
@@ -30270,9 +30271,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I443" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I443" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J443" s="12" t="inlineStr">
@@ -30335,9 +30336,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I444" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I444" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J444" s="12" t="inlineStr">
@@ -30400,9 +30401,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I445" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I445" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J445" s="12" t="inlineStr">
@@ -30465,9 +30466,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I446" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I446" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J446" s="12" t="inlineStr">
@@ -30534,9 +30535,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I447" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I447" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J447" s="12" t="inlineStr">
@@ -30603,9 +30604,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I448" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I448" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J448" s="12" t="inlineStr">
@@ -30672,9 +30673,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I449" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I449" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J449" s="12" t="inlineStr">
@@ -30737,9 +30738,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I450" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I450" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J450" s="12" t="inlineStr">
@@ -30802,9 +30803,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I451" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I451" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J451" s="12" t="inlineStr">
@@ -30871,9 +30872,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I452" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I452" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J452" s="12" t="inlineStr">
@@ -30940,9 +30941,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I453" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I453" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J453" s="12" t="inlineStr">
@@ -31005,9 +31006,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I454" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I454" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J454" s="12" t="inlineStr">
@@ -31074,9 +31075,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I455" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I455" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J455" s="12" t="inlineStr">
@@ -31143,9 +31144,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I456" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I456" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J456" s="12" t="inlineStr">
@@ -31212,9 +31213,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I457" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I457" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J457" s="12" t="inlineStr">
@@ -31281,9 +31282,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I458" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I458" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J458" s="12" t="inlineStr">
@@ -31346,9 +31347,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I459" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I459" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J459" s="12" t="inlineStr">
@@ -31411,9 +31412,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I460" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I460" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J460" s="12" t="inlineStr">
@@ -31476,9 +31477,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I461" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I461" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J461" s="12" t="inlineStr">
@@ -31541,9 +31542,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I462" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I462" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J462" s="12" t="inlineStr">
@@ -31606,9 +31607,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I463" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I463" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J463" s="12" t="inlineStr">
@@ -31671,9 +31672,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I464" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I464" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J464" s="12" t="inlineStr">
@@ -31736,9 +31737,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I465" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I465" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J465" s="12" t="inlineStr">
@@ -31801,9 +31802,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I466" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I466" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J466" s="12" t="inlineStr">
@@ -31866,9 +31867,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I467" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I467" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J467" s="12" t="inlineStr">
@@ -31931,9 +31932,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I468" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I468" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J468" s="12" t="inlineStr">
@@ -31996,9 +31997,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I469" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I469" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J469" s="12" t="inlineStr">
@@ -32191,9 +32192,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I472" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I472" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J472" s="12" t="inlineStr">
@@ -32256,9 +32257,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I473" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I473" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J473" s="12" t="inlineStr">
@@ -32321,9 +32322,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I474" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I474" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J474" s="12" t="inlineStr">
@@ -32386,9 +32387,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I475" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I475" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J475" s="12" t="inlineStr">
@@ -32451,9 +32452,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I476" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I476" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J476" s="12" t="inlineStr">
@@ -32516,9 +32517,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I477" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I477" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J477" s="12" t="inlineStr">
@@ -32581,9 +32582,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I478" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I478" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J478" s="12" t="inlineStr">
@@ -32646,9 +32647,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I479" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I479" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J479" s="12" t="inlineStr">
@@ -32715,9 +32716,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I480" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I480" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J480" s="12" t="inlineStr">
@@ -32784,9 +32785,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I481" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I481" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J481" s="12" t="inlineStr">
@@ -32849,9 +32850,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I482" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I482" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J482" s="12" t="inlineStr">
@@ -32914,9 +32915,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I483" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I483" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J483" s="12" t="inlineStr">
@@ -32979,9 +32980,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I484" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I484" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J484" s="12" t="inlineStr">
@@ -33044,9 +33045,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I485" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I485" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J485" s="12" t="inlineStr">
@@ -33109,9 +33110,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I486" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I486" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J486" s="12" t="inlineStr">
@@ -33239,9 +33240,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I488" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I488" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J488" s="12" t="inlineStr">
@@ -33308,9 +33309,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I489" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I489" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J489" s="12" t="inlineStr">
@@ -33377,9 +33378,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I490" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I490" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J490" s="12" t="inlineStr">
@@ -33446,9 +33447,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I491" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I491" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J491" s="12" t="inlineStr">
@@ -33515,9 +33516,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I492" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I492" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J492" s="12" t="inlineStr">
@@ -33580,9 +33581,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I493" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I493" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J493" s="12" t="inlineStr">
@@ -33645,9 +33646,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I494" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I494" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J494" s="12" t="inlineStr">
@@ -33710,9 +33711,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I495" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I495" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J495" s="12" t="inlineStr">
@@ -33775,9 +33776,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I496" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I496" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J496" s="12" t="inlineStr">
@@ -33840,9 +33841,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I497" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I497" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J497" s="12" t="inlineStr">
@@ -33905,9 +33906,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I498" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I498" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J498" s="12" t="inlineStr">
@@ -33970,9 +33971,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I499" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I499" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J499" s="12" t="inlineStr">
@@ -34035,9 +34036,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I500" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I500" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J500" s="12" t="inlineStr">
@@ -34104,9 +34105,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I501" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I501" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J501" s="13" t="inlineStr">
@@ -34173,9 +34174,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I502" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I502" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J502" s="12" t="inlineStr">
@@ -34238,9 +34239,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I503" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I503" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J503" s="12" t="inlineStr">
@@ -34303,9 +34304,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I504" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I504" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J504" s="12" t="inlineStr">
@@ -34372,9 +34373,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I505" s="10" t="inlineStr">
-        <is>
-          <t>Paul</t>
+      <c r="I505" s="16" t="inlineStr">
+        <is>
+          <t>Paul Strehlenert</t>
         </is>
       </c>
       <c r="J505" s="12" t="inlineStr">
@@ -34441,9 +34442,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I506" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I506" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J506" s="12" t="inlineStr">
@@ -34636,9 +34637,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I509" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I509" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J509" s="12" t="inlineStr">
@@ -34701,9 +34702,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I510" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I510" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J510" s="12" t="inlineStr">
@@ -34896,9 +34897,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I513" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I513" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J513" s="12" t="inlineStr">
@@ -34961,9 +34962,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I514" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I514" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J514" s="12" t="inlineStr">
@@ -35026,9 +35027,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I515" s="10" t="inlineStr">
-        <is>
-          <t>Maria (?)</t>
+      <c r="I515" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson (?)</t>
         </is>
       </c>
       <c r="J515" s="12" t="inlineStr">
@@ -35091,9 +35092,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I516" s="10" t="inlineStr">
-        <is>
-          <t>Maria (?)</t>
+      <c r="I516" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson (?)</t>
         </is>
       </c>
       <c r="J516" s="13" t="inlineStr">
@@ -35156,9 +35157,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I517" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I517" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J517" s="12" t="inlineStr">
@@ -35221,9 +35222,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I518" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I518" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J518" s="13" t="inlineStr">
@@ -35286,9 +35287,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I519" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I519" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J519" s="13" t="inlineStr">
@@ -35351,9 +35352,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I520" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I520" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J520" s="12" t="inlineStr">
@@ -35416,9 +35417,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I521" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I521" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J521" s="13" t="inlineStr">
@@ -35741,9 +35742,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I526" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I526" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J526" s="12" t="inlineStr">
@@ -35806,9 +35807,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I527" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I527" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J527" s="12" t="inlineStr">
@@ -35871,9 +35872,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I528" s="10" t="inlineStr">
-        <is>
-          <t>Janni (?)</t>
+      <c r="I528" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin (?)</t>
         </is>
       </c>
       <c r="J528" s="12" t="inlineStr">
@@ -35936,9 +35937,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I529" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I529" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J529" s="12" t="inlineStr">
@@ -36131,9 +36132,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I532" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I532" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J532" s="12" t="inlineStr">
@@ -36196,9 +36197,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I533" s="10" t="inlineStr">
-        <is>
-          <t>Markus</t>
+      <c r="I533" s="16" t="inlineStr">
+        <is>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="J533" s="12" t="inlineStr">
@@ -36521,9 +36522,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I538" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I538" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J538" s="12" t="inlineStr">
@@ -36586,9 +36587,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I539" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I539" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J539" s="12" t="inlineStr">
@@ -36651,9 +36652,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I540" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I540" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J540" s="12" t="inlineStr">
@@ -36716,9 +36717,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I541" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I541" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J541" s="12" t="inlineStr">
@@ -37037,9 +37038,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I546" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I546" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J546" s="12" t="inlineStr">
@@ -37102,9 +37103,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I547" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I547" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J547" s="12" t="inlineStr">
@@ -37167,9 +37168,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I548" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I548" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J548" s="12" t="inlineStr">
@@ -37232,9 +37233,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I549" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I549" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J549" s="12" t="inlineStr">
@@ -37297,9 +37298,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I550" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I550" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J550" s="12" t="inlineStr">
@@ -37362,9 +37363,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I551" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I551" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J551" s="12" t="inlineStr">
@@ -37549,9 +37550,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I554" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I554" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J554" s="12" t="inlineStr">
@@ -37614,9 +37615,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I555" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I555" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J555" s="12" t="inlineStr">
@@ -37679,9 +37680,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I556" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I556" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J556" s="12" t="inlineStr">
@@ -37744,9 +37745,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I557" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I557" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J557" s="12" t="inlineStr">
@@ -37813,9 +37814,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I558" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I558" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J558" s="12" t="inlineStr">
@@ -37878,9 +37879,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I559" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I559" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J559" s="12" t="inlineStr">
@@ -37943,9 +37944,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I560" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I560" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J560" s="12" t="inlineStr">
@@ -38008,9 +38009,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I561" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I561" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J561" s="13" t="inlineStr">
@@ -38073,9 +38074,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I562" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I562" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J562" s="12" t="inlineStr">
@@ -38138,9 +38139,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I563" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I563" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J563" s="12" t="inlineStr">
@@ -38203,9 +38204,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I564" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I564" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J564" s="12" t="inlineStr">
@@ -38268,9 +38269,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I565" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I565" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J565" s="12" t="inlineStr">
@@ -38333,9 +38334,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I566" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I566" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J566" s="12" t="inlineStr">
@@ -38398,9 +38399,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I567" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I567" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J567" s="12" t="inlineStr">
@@ -38463,9 +38464,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I568" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I568" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J568" s="12" t="inlineStr">
@@ -38528,9 +38529,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I569" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I569" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J569" s="12" t="inlineStr">
@@ -38593,9 +38594,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I570" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I570" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J570" s="12" t="inlineStr">
@@ -38658,9 +38659,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I571" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I571" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J571" s="12" t="inlineStr">
@@ -38723,9 +38724,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I572" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I572" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J572" s="12" t="inlineStr">
@@ -38788,9 +38789,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I573" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I573" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J573" s="12" t="inlineStr">
@@ -38853,9 +38854,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I574" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I574" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J574" s="12" t="inlineStr">
@@ -38918,9 +38919,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I575" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I575" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J575" s="12" t="inlineStr">
@@ -38983,9 +38984,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I576" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I576" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J576" s="12" t="inlineStr">
@@ -39048,9 +39049,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I577" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I577" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J577" s="13" t="inlineStr">
@@ -39113,9 +39114,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I578" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I578" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J578" s="12" t="inlineStr">
@@ -39178,9 +39179,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I579" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I579" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J579" s="12" t="inlineStr">
@@ -39243,9 +39244,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I580" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I580" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J580" s="12" t="inlineStr">
@@ -39308,9 +39309,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I581" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I581" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J581" s="12" t="inlineStr">
@@ -39373,9 +39374,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I582" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I582" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J582" s="12" t="inlineStr">
@@ -39438,9 +39439,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I583" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I583" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J583" s="12" t="inlineStr">
@@ -39503,9 +39504,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I584" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I584" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J584" s="12" t="inlineStr">
@@ -39568,9 +39569,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I585" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I585" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J585" s="12" t="inlineStr">
@@ -39633,9 +39634,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I586" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I586" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J586" s="12" t="inlineStr">
@@ -39698,9 +39699,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I587" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I587" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J587" s="12" t="inlineStr">
@@ -39763,9 +39764,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I588" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I588" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J588" s="12" t="inlineStr">
@@ -39828,9 +39829,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I589" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I589" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J589" s="12" t="inlineStr">
@@ -39893,9 +39894,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I590" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I590" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J590" s="12" t="inlineStr">
@@ -39958,9 +39959,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I591" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I591" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J591" s="13" t="inlineStr">
@@ -40023,9 +40024,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I592" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I592" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J592" s="12" t="inlineStr">
@@ -40088,9 +40089,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I593" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I593" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J593" s="12" t="inlineStr">
@@ -40153,9 +40154,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I594" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I594" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J594" s="12" t="inlineStr">
@@ -40218,9 +40219,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I595" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I595" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J595" s="12" t="inlineStr">
@@ -40466,9 +40467,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I599" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I599" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J599" s="12" t="inlineStr">
@@ -40531,9 +40532,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I600" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I600" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J600" s="12" t="inlineStr">
@@ -40596,9 +40597,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I601" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I601" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J601" s="12" t="inlineStr">
@@ -40661,9 +40662,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I602" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I602" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J602" s="12" t="inlineStr">
@@ -40726,9 +40727,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I603" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I603" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J603" s="13" t="inlineStr">
@@ -40791,9 +40792,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I604" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I604" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J604" s="12" t="inlineStr">
@@ -40856,9 +40857,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I605" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I605" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J605" s="12" t="inlineStr">
@@ -40921,9 +40922,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I606" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I606" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J606" s="12" t="inlineStr">
@@ -40986,9 +40987,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I607" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I607" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J607" s="12" t="inlineStr">
@@ -41055,9 +41056,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I608" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I608" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J608" s="12" t="inlineStr">
@@ -41124,9 +41125,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I609" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I609" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J609" s="12" t="inlineStr">
@@ -41193,9 +41194,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I610" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I610" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J610" s="13" t="inlineStr">
@@ -41258,9 +41259,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I611" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I611" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J611" s="12" t="inlineStr">
@@ -41518,9 +41519,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I615" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I615" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J615" s="12" t="inlineStr">
@@ -41583,9 +41584,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I616" s="10" t="inlineStr">
-        <is>
-          <t>Janni</t>
+      <c r="I616" s="16" t="inlineStr">
+        <is>
+          <t>Janni Servin</t>
         </is>
       </c>
       <c r="J616" s="13" t="inlineStr">
@@ -41648,9 +41649,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I617" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I617" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J617" s="12" t="inlineStr">
@@ -41713,9 +41714,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I618" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I618" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J618" s="12" t="inlineStr">
@@ -41778,9 +41779,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I619" s="10" t="inlineStr">
-        <is>
-          <t>Martin</t>
+      <c r="I619" s="16" t="inlineStr">
+        <is>
+          <t>Martin Lindqvist</t>
         </is>
       </c>
       <c r="J619" s="12" t="inlineStr">
@@ -41908,9 +41909,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I621" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I621" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J621" s="13" t="inlineStr">
@@ -41973,9 +41974,9 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="I622" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I622" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J622" s="12" t="inlineStr">
@@ -42038,9 +42039,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I623" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I623" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J623" s="12" t="inlineStr">
@@ -42164,9 +42165,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I625" s="10" t="inlineStr">
-        <is>
-          <t>Sari</t>
+      <c r="I625" s="16" t="inlineStr">
+        <is>
+          <t>Sari Roponen</t>
         </is>
       </c>
       <c r="J625" s="12" t="inlineStr">
@@ -42229,9 +42230,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I626" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I626" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J626" s="12" t="inlineStr">
@@ -42294,9 +42295,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I627" s="10" t="inlineStr">
-        <is>
-          <t>Maria</t>
+      <c r="I627" s="16" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="J627" s="12" t="inlineStr">
@@ -42428,9 +42429,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I629" s="10" t="inlineStr">
-        <is>
-          <t>Kristoffer</t>
+      <c r="I629" s="16" t="inlineStr">
+        <is>
+          <t>Kristoffer Almqvist</t>
         </is>
       </c>
       <c r="J629" s="12" t="inlineStr">
@@ -42493,9 +42494,9 @@
           <t>Nej</t>
         </is>
       </c>
-      <c r="I630" s="10" t="inlineStr">
-        <is>
-          <t>Per</t>
+      <c r="I630" s="16" t="inlineStr">
+        <is>
+          <t>Per Folkesson</t>
         </is>
       </c>
       <c r="J630" s="13" t="inlineStr">
@@ -42576,622 +42577,1090 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J268" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K269" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K270" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J274" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K274" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K275" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K276" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J277" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K277" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J278" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K278" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J279" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J280" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K280" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J281" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J282" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J283" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K308" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K309" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K317" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K318" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K319" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J334" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K334" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K335" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J336" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J339" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J349" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J353" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J362" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J363" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J365" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K397" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K398" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K423" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K424" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J433" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J436" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J437" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K437" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J438" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K446" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K447" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K448" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K451" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K452" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J453" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K454" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J455" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K455" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K456" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K457" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J468" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K470" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K471" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K479" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K480" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J485" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J486" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J487" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J488" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K488" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J489" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K489" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J490" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K490" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J491" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K491" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J492" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J493" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J494" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J495" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J496" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J497" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J498" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J499" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J500" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K500" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K501" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J502" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J503" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K504" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J505" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K505" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J506" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J507" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J508" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J509" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J520" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J522" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K522" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J523" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K523" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K524" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K525" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J526" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J527" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J528" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J529" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J532" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J533" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J534" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J535" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J536" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J537" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J538" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J539" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J546" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J547" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J548" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J549" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J550" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J551" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K557" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J563" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J564" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J565" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J581" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J582" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J583" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J584" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J585" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J586" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J590" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J592" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J593" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J601" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J602" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J604" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J605" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J606" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J607" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K607" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J608" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K608" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J609" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K609" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J611" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J615" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J617" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J618" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J619" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J620" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J622" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J623" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J624" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J625" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J626" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J627" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J628" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K628" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J629" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K244" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K245" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K246" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K247" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K265" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K266" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K267" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J268" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K268" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K269" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K270" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K273" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J274" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K274" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K275" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K276" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J277" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K277" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J278" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K278" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J279" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K279" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J280" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K280" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J281" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J282" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J283" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K305" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K306" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K307" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K308" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K309" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K317" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K318" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K319" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I332" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J334" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K334" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K335" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J336" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J339" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K340" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K341" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K342" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I346" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I348" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J349" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J353" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K355" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I357" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I361" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I362" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J362" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J363" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I364" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I365" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J365" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I367" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I368" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I369" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I370" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I374" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I375" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K375" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K376" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I377" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I378" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I379" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I381" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K381" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K382" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K383" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K384" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I388" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K388" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K389" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K390" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I392" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I393" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K393" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K394" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K395" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K396" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K397" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K398" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K399" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I400" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K400" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I402" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I403" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I405" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I406" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I413" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I414" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I417" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I421" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I423" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K423" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K424" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I425" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I426" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I429" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I433" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J433" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I435" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J436" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K436" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J437" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K437" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J438" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K438" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I439" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I441" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I442" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I443" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I446" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K446" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I447" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K447" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I448" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K448" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I449" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I451" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K451" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K452" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I453" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J453" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K454" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I455" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J455" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K455" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K456" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K457" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I462" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I465" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I466" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I467" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I468" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J468" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I469" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K470" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K471" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I472" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I473" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I475" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I477" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K479" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K480" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I481" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I482" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I483" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I484" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I485" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J485" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I486" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J486" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J487" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I488" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J488" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K488" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I489" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J489" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K489" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I490" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J490" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K490" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J491" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K491" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I492" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J492" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I493" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J493" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I494" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J494" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I495" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J495" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I496" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J496" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J497" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I498" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J498" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I499" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J499" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I500" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J500" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K500" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K501" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J502" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J503" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K504" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I505" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J505" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K505" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J506" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J507" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J508" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I509" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J509" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I510" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I514" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I515" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I516" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I518" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J520" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I521" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J522" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K522" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J523" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K523" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K524" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K525" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I526" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J526" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I527" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J527" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I528" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J528" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I529" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J529" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I532" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J532" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I533" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J533" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J534" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J535" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J536" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J537" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I538" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J538" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I539" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J539" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I540" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I541" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I546" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J546" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I547" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J547" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I548" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J548" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I549" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J549" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I550" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J550" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I551" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J551" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I554" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I555" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I556" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I557" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K557" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I558" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I559" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J559" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I560" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J560" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I561" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I562" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J562" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I563" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J563" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I564" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J564" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I565" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J565" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I566" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J566" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I567" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J567" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I568" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J568" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I569" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J569" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I570" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J570" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I571" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J571" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I572" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J572" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I573" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J573" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I574" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J574" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I575" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J575" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I576" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J576" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I577" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I578" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J578" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I579" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J579" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I580" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J580" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I581" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J581" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I582" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J582" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I583" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J583" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I584" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J584" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I585" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J585" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I586" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J586" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I587" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J587" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I588" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J588" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I589" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J589" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I590" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J590" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I591" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I592" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J592" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I593" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J593" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I594" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J594" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I595" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J595" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J596" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I599" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J599" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I600" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J600" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I601" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J601" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I602" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J602" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I603" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I604" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J604" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I605" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J605" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I606" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J606" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I607" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J607" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K607" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I608" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J608" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K608" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I609" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J609" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K609" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I610" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I611" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J611" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I615" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J615" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I616" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I617" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J617" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I618" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J618" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I619" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J619" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J620" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I621" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I622" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J622" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I623" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J623" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J624" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I625" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J625" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I626" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J626" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I627" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J627" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J628" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K628" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I629" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J629" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I630" r:id="rId1099"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -43228,253 +43697,253 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Kodlistor – källa till rullistorna i Blankett. Redigera inte.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Tillstånd</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Hävdstatus</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Grund för bedömning</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>Livsmiljötyp, behov av justering</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Utbredning, behov av justering</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>Vad ska kontrolleras</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Metod för kontroll</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>Ja/Nej</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Gott</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Aktiv hävd pågår</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Eget fältbesök</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Inget behov av justering</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Inget behov av justering</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Typiska och karakteristiska arter</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Fältbesök</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Icke gott</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Hävd har upphört</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Standardiserad inventering (uppföljning/ÄoB)</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Ändring till annan livsmiljötyp</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Yttergränser, kvalitetsförbättring</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Strukturer</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>Fältinventering (standardiserad metodik)</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Okänt – kan ej bedöma</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Hävd men otillräcklig</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Skötselplan eller bevarandeplan</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Ändring till utvecklingsmark</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Yttergränser, ändrad utbredning</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>Hävd</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>Skrivbord / Granska mot andra underlag</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>Vet ej</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Blandat – se andelar</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Ej hävdberoende</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Konsultrapport eller PM</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Osäker – kan ej bedöma om livsmiljötyp eller inte</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Behov av att dela upp ytan, flera livsmiljötyper</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>Funktioner (hydrologi, störningar)</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>Annan metod</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Vet ej</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Betesstöd / jordbruksblock</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Obestämd – kan ej bedöma vilken livsmiljötyp</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Morfologi (jordart, formationer)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Allmän lokalkännedom</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Annan negativ påverkan</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Ingen grund – osäker</t>
         </is>
@@ -43519,7 +43988,7 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Åtgärdas-ytor — basinventeringens öppna kunskapsluckor</t>
         </is>
@@ -43598,10 +44067,10 @@
           <t>Trädklädd betesmark</t>
         </is>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="22" t="n">
         <v>24.95</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -43632,10 +44101,10 @@
           <t>Strandängar vid Östersjön</t>
         </is>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <v>6.24</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -43666,10 +44135,10 @@
           <t>Obestämd torr-frisk hed/gräsmark nedanför trädgränsen (4810)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="22" t="n">
         <v>2.62</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -43700,10 +44169,10 @@
           <t>Hällmarkstorräng</t>
         </is>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <v>1.47</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -43734,10 +44203,10 @@
           <t>Trädklädd betesmark - Ädellövdominerade trädklädda betesmarker</t>
         </is>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="22" t="n">
         <v>1.91</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -43768,10 +44237,10 @@
           <t>Hällmarkstorräng - Hällmarkstorrängstyp</t>
         </is>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>3.96</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -43802,10 +44271,10 @@
           <t>Trädklädd betesmark - Ekhagar</t>
         </is>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="22" t="n">
         <v>3.08</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -43836,10 +44305,10 @@
           <t>Icke-natura skog</t>
         </is>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>0.43</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -43870,10 +44339,10 @@
           <t>Obestämd fuktig - blöt hed/gräsmark/myrmark nedanför trädgränsen (4811)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="22" t="n">
         <v>0.97</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -43904,10 +44373,10 @@
           <t>Taiga</t>
         </is>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="22" t="n">
         <v>1.55</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -43938,10 +44407,10 @@
           <t>Slåtterängar i låglandet</t>
         </is>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="22" t="n">
         <v>0.14</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -43972,10 +44441,10 @@
           <t>Gräsmarker, substratdominerade gräsmarker och alluviala gräsmarker nedanför barrskogsgrä</t>
         </is>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="22" t="n">
         <v>0.33</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -44006,10 +44475,10 @@
           <t>Osäker Taiga/ickenatura-skog</t>
         </is>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="22" t="n">
         <v>0.23</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -44040,10 +44509,10 @@
           <t>Enbuskmarker - Naturlig enbuskmark vid kust</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n">
+      <c r="F22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="22" t="n">
         <v>0.32</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -44074,10 +44543,10 @@
           <t>Silikatgräsmarker</t>
         </is>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -44108,10 +44577,10 @@
           <t>Strandängar vid Östersjön</t>
         </is>
       </c>
-      <c r="F24" s="20" t="n">
+      <c r="F24" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="22" t="n">
         <v>22.21</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -44142,10 +44611,10 @@
           <t>Öppen kultiverad gräsmark</t>
         </is>
       </c>
-      <c r="F25" s="20" t="n">
+      <c r="F25" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="22" t="n">
         <v>9.19</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -44176,10 +44645,10 @@
           <t>Silikatgräsmarker</t>
         </is>
       </c>
-      <c r="F26" s="20" t="n">
+      <c r="F26" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="22" t="n">
         <v>2.04</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -44210,10 +44679,10 @@
           <t>Trädklädd betesmark</t>
         </is>
       </c>
-      <c r="F27" s="20" t="n">
+      <c r="F27" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="22" t="n">
         <v>2.49</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -44244,10 +44713,10 @@
           <t>Obestämd torr-frisk hed/gräsmark nedanför trädgränsen (4810)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="22" t="n">
         <v>2.71</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -44278,10 +44747,10 @@
           <t>Trädklädd betesmark</t>
         </is>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="22" t="n">
         <v>1.79</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -44312,10 +44781,10 @@
           <t>Näringsfattiga slättsjöar</t>
         </is>
       </c>
-      <c r="F30" s="20" t="n">
+      <c r="F30" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="22" t="n">
         <v>49.94</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -44346,10 +44815,10 @@
           <t>Gräsmarker, substratdominerade gräsmarker och alluviala gräsmarker nedanför barrskogsgrä</t>
         </is>
       </c>
-      <c r="F31" s="20" t="n">
+      <c r="F31" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="22" t="n">
         <v>0.73</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -44380,10 +44849,10 @@
           <t>Öppna mossar och kärr - Kärr och gungflyn</t>
         </is>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F32" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -44414,10 +44883,10 @@
           <t>Trädklädd betesmark</t>
         </is>
       </c>
-      <c r="F33" s="20" t="n">
+      <c r="F33" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="22" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -44448,10 +44917,10 @@
           <t>Strandängar vid Östersjön</t>
         </is>
       </c>
-      <c r="F34" s="20" t="n">
+      <c r="F34" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="22" t="n">
         <v>1.25</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -44482,10 +44951,10 @@
           <t>Hällmarkstorräng - Hällmarkstorrängstyp</t>
         </is>
       </c>
-      <c r="F35" s="20" t="n">
+      <c r="F35" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="22" t="n">
         <v>0.65</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -44516,10 +44985,10 @@
           <t>Lövsumpskog</t>
         </is>
       </c>
-      <c r="F36" s="20" t="n">
+      <c r="F36" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="22" t="n">
         <v>1.56</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -44550,10 +45019,10 @@
           <t>Taiga</t>
         </is>
       </c>
-      <c r="F37" s="20" t="n">
+      <c r="F37" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="22" t="n">
         <v>26.39</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -44584,10 +45053,10 @@
           <t>Högmossar</t>
         </is>
       </c>
-      <c r="F38" s="20" t="n">
+      <c r="F38" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="22" t="n">
         <v>12.56</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -44598,22 +45067,22 @@
       <c r="I38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>Summa</t>
         </is>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="24">
         <f>SUM(F9:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="25">
         <f>SUM(G9:G38)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Källa: NNK_YTA ur Naturtypskartan_D (publik Natura naturtypskarta), filtrerat på karteringsstatus 5 – Åtgärdas. Områdestillhörighet framtagen med scripts/analysis/koppla_omraden.py: överlappsbaserad koppling mot det rikstäckande SCI-lagret från Naturvårdsregistret. Samtliga 141 ytor ligger inom Natura 2000. Orange markering i kolumnen Livsmiljötyp = hävdberoende livsmiljötyp.</t>
         </is>
@@ -44659,7 +45128,7 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Från blankett till granskningslager till NNK</t>
         </is>
@@ -44960,44 +45429,44 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>(sätts av dig, ej i blanketten)</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>KARTERINGSSTATUS</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>2 Granskad vid skrivbordet för förvaltarkunskap och dokument. 3 Besökt i fält om förvaltaren faktiskt varit där nyligen. 4 Inventerad i fält endast vid standardiserad metodik.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>(sätts av dig, ej i blanketten)</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>FÖRÄNDRINGSORSAK</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>3 Komplettering när kunskapen fanns men aldrig registrerats. 1 Rättning vid felaktig kartering. 2 Faktisk förändring endast när naturen faktiskt förändrats.</t>
         </is>

--- a/blanketter/blankett_forvaltarkunskap_nnk.xlsx
+++ b/blanketter/blankett_forvaltarkunskap_nnk.xlsx
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C32"/>
+  <dimension ref="B2:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -741,7 +741,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.5, 2026-08-27</t>
+          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.6, 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -881,113 +881,125 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nytt sedan version 1.6: rader grupperade per objekt. Ett objekt med flera naturtyper visar bara sin första rad — klicka på [+] i vänstermarginalen (eller Disposition-fliken i Excel) för att fälla ut de övriga naturtyprader som hör till samma objekt. Gör bara blanketten kortare att bläddra i, ändrar ingen data. Om du filtrerar (punkt 1): fäll ut grupperna innan du filtrerar, annars kan dolda naturtyprader missas i urvalet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Tre regler att ha med sig i samtalet</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="42" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>En igenvuxen äng är fortfarande en äng. Om orsaken är utebliven skötsel ska livsmiljötypen stå kvar och tillståndet sättas till Icke gott — inte klassas om till annan naturtyp. (Lathunden, "Vad kan vi ändra på?")</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Kunskap som funnits men aldrig registrerats är en Komplettering, inte en Faktisk förändring. Det avgör om länet rapporterar in en arealförändring som aldrig hänt. (Handledningen 5.4)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kunskap som funnits men aldrig registrerats är en Komplettering, inte en Faktisk förändring. Det avgör om länet rapporterar in en arealförändring som aldrig hänt. (Handledningen 5.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Fråga alltid efter årtal. Utan datering går FAQ fråga 4:s krav på "hur aktuell bedömningen är" inte att besvara.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Flikar</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Blankett</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>628 rader, en per objekt × livsmiljötyp. Sorterad med prioritet 1 först.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Åtgärdas-ytor</t>
+          <t>Blankett</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>De 141 ytor med karteringsstatus 5, per objekt och livsmiljötyp.</t>
+          <t>628 rader, en per objekt × livsmiljötyp. Sorterad med prioritet 1 först.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Kodlistor</t>
+          <t>Åtgärdas-ytor</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tillåtna värden. Källa till rullistorna — redigera inte.</t>
+          <t>De 141 ytor med karteringsstatus 5, per objekt och livsmiljötyp.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Kodlistor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Tillåtna värden. Källa till rullistorna — redigera inte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>Fältmappning</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Vilken blankettkolumn som hamnar i vilket fält i granskningslagret och NNK.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Källor</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="2" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Förifylld areal och objektsurval: NNK-statistik per Natura 2000-område D-län, uttag 2026-01-20 (Naturvårdsverket). Åtgärdas-ytorna: NNK-lagrets attributtabell, uttag från ArcGIS Pro 2026-08-17. Kodvärden: Handledning för NNK 2026-07-03 samt Lathund granskning WebbGIS-KartLitS 2026-07-10.</t>
         </is>
@@ -996,14 +1008,14 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B9:C9"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1023,7 +1035,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y630"/>
@@ -1357,7 +1369,7 @@
       <c r="X3" s="15" t="n"/>
       <c r="Y3" s="15" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" hidden="1" outlineLevel="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1418,7 +1430,7 @@
       <c r="X4" s="15" t="n"/>
       <c r="Y4" s="15" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" hidden="1" outlineLevel="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1479,7 +1491,7 @@
       <c r="X5" s="15" t="n"/>
       <c r="Y5" s="15" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" hidden="1" outlineLevel="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1540,7 +1552,7 @@
       <c r="X6" s="15" t="n"/>
       <c r="Y6" s="15" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" hidden="1" outlineLevel="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1601,7 +1613,7 @@
       <c r="X7" s="15" t="n"/>
       <c r="Y7" s="15" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" hidden="1" outlineLevel="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1662,7 +1674,7 @@
       <c r="X8" s="15" t="n"/>
       <c r="Y8" s="15" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" hidden="1" outlineLevel="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1723,7 +1735,7 @@
       <c r="X9" s="15" t="n"/>
       <c r="Y9" s="15" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" hidden="1" outlineLevel="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1784,7 +1796,7 @@
       <c r="X10" s="15" t="n"/>
       <c r="Y10" s="15" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" hidden="1" outlineLevel="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1845,7 +1857,7 @@
       <c r="X11" s="15" t="n"/>
       <c r="Y11" s="15" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" hidden="1" outlineLevel="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1906,7 +1918,7 @@
       <c r="X12" s="15" t="n"/>
       <c r="Y12" s="15" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" hidden="1" outlineLevel="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -1967,7 +1979,7 @@
       <c r="X13" s="15" t="n"/>
       <c r="Y13" s="15" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" hidden="1" outlineLevel="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2028,7 +2040,7 @@
       <c r="X14" s="15" t="n"/>
       <c r="Y14" s="15" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2089,7 +2101,7 @@
       <c r="X15" s="15" t="n"/>
       <c r="Y15" s="15" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" hidden="1" outlineLevel="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2150,7 +2162,7 @@
       <c r="X16" s="15" t="n"/>
       <c r="Y16" s="15" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" hidden="1" outlineLevel="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2211,7 +2223,7 @@
       <c r="X17" s="15" t="n"/>
       <c r="Y17" s="15" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" hidden="1" outlineLevel="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2272,7 +2284,7 @@
       <c r="X18" s="15" t="n"/>
       <c r="Y18" s="15" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" hidden="1" outlineLevel="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2333,7 +2345,7 @@
       <c r="X19" s="15" t="n"/>
       <c r="Y19" s="15" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" hidden="1" outlineLevel="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2394,7 +2406,7 @@
       <c r="X20" s="15" t="n"/>
       <c r="Y20" s="15" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" hidden="1" outlineLevel="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2455,7 +2467,7 @@
       <c r="X21" s="15" t="n"/>
       <c r="Y21" s="15" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" hidden="1" outlineLevel="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2516,7 +2528,7 @@
       <c r="X22" s="15" t="n"/>
       <c r="Y22" s="15" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" hidden="1" outlineLevel="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2577,7 +2589,7 @@
       <c r="X23" s="15" t="n"/>
       <c r="Y23" s="15" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" hidden="1" outlineLevel="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2638,7 +2650,7 @@
       <c r="X24" s="15" t="n"/>
       <c r="Y24" s="15" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" hidden="1" outlineLevel="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2699,7 +2711,7 @@
       <c r="X25" s="15" t="n"/>
       <c r="Y25" s="15" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" hidden="1" outlineLevel="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2760,7 +2772,7 @@
       <c r="X26" s="15" t="n"/>
       <c r="Y26" s="15" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" hidden="1" outlineLevel="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2821,7 +2833,7 @@
       <c r="X27" s="15" t="n"/>
       <c r="Y27" s="15" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" hidden="1" outlineLevel="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -2882,7 +2894,7 @@
       <c r="X28" s="15" t="n"/>
       <c r="Y28" s="15" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" hidden="1" outlineLevel="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3008,7 +3020,7 @@
       <c r="X30" s="15" t="n"/>
       <c r="Y30" s="15" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" hidden="1" outlineLevel="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3073,7 +3085,7 @@
       <c r="X31" s="15" t="n"/>
       <c r="Y31" s="15" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" hidden="1" outlineLevel="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3138,7 +3150,7 @@
       <c r="X32" s="15" t="n"/>
       <c r="Y32" s="15" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" hidden="1" outlineLevel="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3203,7 +3215,7 @@
       <c r="X33" s="15" t="n"/>
       <c r="Y33" s="15" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" hidden="1" outlineLevel="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3268,7 +3280,7 @@
       <c r="X34" s="15" t="n"/>
       <c r="Y34" s="15" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" hidden="1" outlineLevel="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3333,7 +3345,7 @@
       <c r="X35" s="15" t="n"/>
       <c r="Y35" s="15" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" hidden="1" outlineLevel="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3398,7 +3410,7 @@
       <c r="X36" s="15" t="n"/>
       <c r="Y36" s="15" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" hidden="1" outlineLevel="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3463,7 +3475,7 @@
       <c r="X37" s="15" t="n"/>
       <c r="Y37" s="15" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" hidden="1" outlineLevel="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3528,7 +3540,7 @@
       <c r="X38" s="15" t="n"/>
       <c r="Y38" s="15" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" hidden="1" outlineLevel="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3593,7 +3605,7 @@
       <c r="X39" s="15" t="n"/>
       <c r="Y39" s="15" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" hidden="1" outlineLevel="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3658,7 +3670,7 @@
       <c r="X40" s="15" t="n"/>
       <c r="Y40" s="15" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" hidden="1" outlineLevel="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3723,7 +3735,7 @@
       <c r="X41" s="15" t="n"/>
       <c r="Y41" s="15" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" hidden="1" outlineLevel="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3788,7 +3800,7 @@
       <c r="X42" s="15" t="n"/>
       <c r="Y42" s="15" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" hidden="1" outlineLevel="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3853,7 +3865,7 @@
       <c r="X43" s="15" t="n"/>
       <c r="Y43" s="15" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" hidden="1" outlineLevel="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3918,7 +3930,7 @@
       <c r="X44" s="15" t="n"/>
       <c r="Y44" s="15" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" hidden="1" outlineLevel="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -3983,7 +3995,7 @@
       <c r="X45" s="15" t="n"/>
       <c r="Y45" s="15" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" hidden="1" outlineLevel="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4048,7 +4060,7 @@
       <c r="X46" s="15" t="n"/>
       <c r="Y46" s="15" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" hidden="1" outlineLevel="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4182,7 +4194,7 @@
       <c r="X48" s="15" t="n"/>
       <c r="Y48" s="15" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" hidden="1" outlineLevel="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4251,7 +4263,7 @@
       <c r="X49" s="15" t="n"/>
       <c r="Y49" s="15" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" hidden="1" outlineLevel="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4320,7 +4332,7 @@
       <c r="X50" s="15" t="n"/>
       <c r="Y50" s="15" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" hidden="1" outlineLevel="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4389,7 +4401,7 @@
       <c r="X51" s="15" t="n"/>
       <c r="Y51" s="15" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" hidden="1" outlineLevel="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4458,7 +4470,7 @@
       <c r="X52" s="15" t="n"/>
       <c r="Y52" s="15" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" outlineLevel="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4527,7 +4539,7 @@
       <c r="X53" s="15" t="n"/>
       <c r="Y53" s="15" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" outlineLevel="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4596,7 +4608,7 @@
       <c r="X54" s="15" t="n"/>
       <c r="Y54" s="15" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" outlineLevel="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4665,7 +4677,7 @@
       <c r="X55" s="15" t="n"/>
       <c r="Y55" s="15" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" outlineLevel="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4734,7 +4746,7 @@
       <c r="X56" s="15" t="n"/>
       <c r="Y56" s="15" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" outlineLevel="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4803,7 +4815,7 @@
       <c r="X57" s="15" t="n"/>
       <c r="Y57" s="15" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" hidden="1" outlineLevel="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4872,7 +4884,7 @@
       <c r="X58" s="15" t="n"/>
       <c r="Y58" s="15" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" outlineLevel="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -4941,7 +4953,7 @@
       <c r="X59" s="15" t="n"/>
       <c r="Y59" s="15" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" outlineLevel="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5010,7 +5022,7 @@
       <c r="X60" s="15" t="n"/>
       <c r="Y60" s="15" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" hidden="1" outlineLevel="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5144,7 +5156,7 @@
       <c r="X62" s="15" t="n"/>
       <c r="Y62" s="15" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" outlineLevel="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5209,7 +5221,7 @@
       <c r="X63" s="15" t="n"/>
       <c r="Y63" s="15" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1" outlineLevel="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5274,7 +5286,7 @@
       <c r="X64" s="15" t="n"/>
       <c r="Y64" s="15" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" hidden="1" outlineLevel="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5339,7 +5351,7 @@
       <c r="X65" s="15" t="n"/>
       <c r="Y65" s="15" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" hidden="1" outlineLevel="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5404,7 +5416,7 @@
       <c r="X66" s="15" t="n"/>
       <c r="Y66" s="15" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" hidden="1" outlineLevel="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5469,7 +5481,7 @@
       <c r="X67" s="15" t="n"/>
       <c r="Y67" s="15" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" hidden="1" outlineLevel="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5534,7 +5546,7 @@
       <c r="X68" s="15" t="n"/>
       <c r="Y68" s="15" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" hidden="1" outlineLevel="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5599,7 +5611,7 @@
       <c r="X69" s="15" t="n"/>
       <c r="Y69" s="15" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" hidden="1" outlineLevel="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5664,7 +5676,7 @@
       <c r="X70" s="15" t="n"/>
       <c r="Y70" s="15" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" hidden="1" outlineLevel="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5729,7 +5741,7 @@
       <c r="X71" s="15" t="n"/>
       <c r="Y71" s="15" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" hidden="1" outlineLevel="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5794,7 +5806,7 @@
       <c r="X72" s="15" t="n"/>
       <c r="Y72" s="15" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" hidden="1" outlineLevel="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5859,7 +5871,7 @@
       <c r="X73" s="15" t="n"/>
       <c r="Y73" s="15" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" hidden="1" outlineLevel="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5924,7 +5936,7 @@
       <c r="X74" s="15" t="n"/>
       <c r="Y74" s="15" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" hidden="1" outlineLevel="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -5989,7 +6001,7 @@
       <c r="X75" s="15" t="n"/>
       <c r="Y75" s="15" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" hidden="1" outlineLevel="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6054,7 +6066,7 @@
       <c r="X76" s="15" t="n"/>
       <c r="Y76" s="15" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" hidden="1" outlineLevel="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6119,7 +6131,7 @@
       <c r="X77" s="15" t="n"/>
       <c r="Y77" s="15" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" hidden="1" outlineLevel="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6184,7 +6196,7 @@
       <c r="X78" s="15" t="n"/>
       <c r="Y78" s="15" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" hidden="1" outlineLevel="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6314,7 +6326,7 @@
       <c r="X80" s="15" t="n"/>
       <c r="Y80" s="15" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" hidden="1" outlineLevel="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6379,7 +6391,7 @@
       <c r="X81" s="15" t="n"/>
       <c r="Y81" s="15" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" hidden="1" outlineLevel="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6444,7 +6456,7 @@
       <c r="X82" s="15" t="n"/>
       <c r="Y82" s="15" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" hidden="1" outlineLevel="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6509,7 +6521,7 @@
       <c r="X83" s="15" t="n"/>
       <c r="Y83" s="15" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" hidden="1" outlineLevel="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6574,7 +6586,7 @@
       <c r="X84" s="15" t="n"/>
       <c r="Y84" s="15" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" hidden="1" outlineLevel="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6639,7 +6651,7 @@
       <c r="X85" s="15" t="n"/>
       <c r="Y85" s="15" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" hidden="1" outlineLevel="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6704,7 +6716,7 @@
       <c r="X86" s="15" t="n"/>
       <c r="Y86" s="15" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" hidden="1" outlineLevel="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6834,7 +6846,7 @@
       <c r="X88" s="15" t="n"/>
       <c r="Y88" s="15" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" hidden="1" outlineLevel="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6899,7 +6911,7 @@
       <c r="X89" s="15" t="n"/>
       <c r="Y89" s="15" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" hidden="1" outlineLevel="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -6964,7 +6976,7 @@
       <c r="X90" s="15" t="n"/>
       <c r="Y90" s="15" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" hidden="1" outlineLevel="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7029,7 +7041,7 @@
       <c r="X91" s="15" t="n"/>
       <c r="Y91" s="15" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" hidden="1" outlineLevel="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7094,7 +7106,7 @@
       <c r="X92" s="15" t="n"/>
       <c r="Y92" s="15" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" hidden="1" outlineLevel="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7159,7 +7171,7 @@
       <c r="X93" s="15" t="n"/>
       <c r="Y93" s="15" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" hidden="1" outlineLevel="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7224,7 +7236,7 @@
       <c r="X94" s="15" t="n"/>
       <c r="Y94" s="15" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" hidden="1" outlineLevel="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7289,7 +7301,7 @@
       <c r="X95" s="15" t="n"/>
       <c r="Y95" s="15" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" hidden="1" outlineLevel="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7354,7 +7366,7 @@
       <c r="X96" s="15" t="n"/>
       <c r="Y96" s="15" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" hidden="1" outlineLevel="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7419,7 +7431,7 @@
       <c r="X97" s="15" t="n"/>
       <c r="Y97" s="15" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" hidden="1" outlineLevel="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7484,7 +7496,7 @@
       <c r="X98" s="15" t="n"/>
       <c r="Y98" s="15" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" hidden="1" outlineLevel="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7614,7 +7626,7 @@
       <c r="X100" s="15" t="n"/>
       <c r="Y100" s="15" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" hidden="1" outlineLevel="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7679,7 +7691,7 @@
       <c r="X101" s="15" t="n"/>
       <c r="Y101" s="15" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" hidden="1" outlineLevel="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7813,7 +7825,7 @@
       <c r="X103" s="15" t="n"/>
       <c r="Y103" s="15" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" hidden="1" outlineLevel="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7882,7 +7894,7 @@
       <c r="X104" s="15" t="n"/>
       <c r="Y104" s="15" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" hidden="1" outlineLevel="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -7951,7 +7963,7 @@
       <c r="X105" s="15" t="n"/>
       <c r="Y105" s="15" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" hidden="1" outlineLevel="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8020,7 +8032,7 @@
       <c r="X106" s="15" t="n"/>
       <c r="Y106" s="15" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" hidden="1" outlineLevel="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8089,7 +8101,7 @@
       <c r="X107" s="15" t="n"/>
       <c r="Y107" s="15" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" hidden="1" outlineLevel="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8227,7 +8239,7 @@
       <c r="X109" s="15" t="n"/>
       <c r="Y109" s="15" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" hidden="1" outlineLevel="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8296,7 +8308,7 @@
       <c r="X110" s="15" t="n"/>
       <c r="Y110" s="15" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" hidden="1" outlineLevel="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8365,7 +8377,7 @@
       <c r="X111" s="15" t="n"/>
       <c r="Y111" s="15" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" hidden="1" outlineLevel="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8434,7 +8446,7 @@
       <c r="X112" s="15" t="n"/>
       <c r="Y112" s="15" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" hidden="1" outlineLevel="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8503,7 +8515,7 @@
       <c r="X113" s="15" t="n"/>
       <c r="Y113" s="15" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" hidden="1" outlineLevel="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8572,7 +8584,7 @@
       <c r="X114" s="15" t="n"/>
       <c r="Y114" s="15" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" hidden="1" outlineLevel="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8641,7 +8653,7 @@
       <c r="X115" s="15" t="n"/>
       <c r="Y115" s="15" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" hidden="1" outlineLevel="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8710,7 +8722,7 @@
       <c r="X116" s="15" t="n"/>
       <c r="Y116" s="15" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" hidden="1" outlineLevel="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8779,7 +8791,7 @@
       <c r="X117" s="15" t="n"/>
       <c r="Y117" s="15" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" hidden="1" outlineLevel="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8848,7 +8860,7 @@
       <c r="X118" s="15" t="n"/>
       <c r="Y118" s="15" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" hidden="1" outlineLevel="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8917,7 +8929,7 @@
       <c r="X119" s="15" t="n"/>
       <c r="Y119" s="15" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" hidden="1" outlineLevel="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -8986,7 +8998,7 @@
       <c r="X120" s="15" t="n"/>
       <c r="Y120" s="15" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" hidden="1" outlineLevel="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9120,7 +9132,7 @@
       <c r="X122" s="15" t="n"/>
       <c r="Y122" s="15" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" hidden="1" outlineLevel="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9185,7 +9197,7 @@
       <c r="X123" s="15" t="n"/>
       <c r="Y123" s="15" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" hidden="1" outlineLevel="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9250,7 +9262,7 @@
       <c r="X124" s="15" t="n"/>
       <c r="Y124" s="15" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" hidden="1" outlineLevel="1">
       <c r="A125" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9315,7 +9327,7 @@
       <c r="X125" s="15" t="n"/>
       <c r="Y125" s="15" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" hidden="1" outlineLevel="1">
       <c r="A126" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9514,7 +9526,7 @@
       <c r="X128" s="15" t="n"/>
       <c r="Y128" s="15" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" hidden="1" outlineLevel="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9583,7 +9595,7 @@
       <c r="X129" s="15" t="n"/>
       <c r="Y129" s="15" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" hidden="1" outlineLevel="1">
       <c r="A130" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9652,7 +9664,7 @@
       <c r="X130" s="15" t="n"/>
       <c r="Y130" s="15" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" hidden="1" outlineLevel="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9721,7 +9733,7 @@
       <c r="X131" s="15" t="n"/>
       <c r="Y131" s="15" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" hidden="1" outlineLevel="1">
       <c r="A132" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9790,7 +9802,7 @@
       <c r="X132" s="15" t="n"/>
       <c r="Y132" s="15" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" hidden="1" outlineLevel="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9859,7 +9871,7 @@
       <c r="X133" s="15" t="n"/>
       <c r="Y133" s="15" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" hidden="1" outlineLevel="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9928,7 +9940,7 @@
       <c r="X134" s="15" t="n"/>
       <c r="Y134" s="15" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" hidden="1" outlineLevel="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -9997,7 +10009,7 @@
       <c r="X135" s="15" t="n"/>
       <c r="Y135" s="15" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" hidden="1" outlineLevel="1">
       <c r="A136" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10131,7 +10143,7 @@
       <c r="X137" s="15" t="n"/>
       <c r="Y137" s="15" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" hidden="1" outlineLevel="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10196,7 +10208,7 @@
       <c r="X138" s="15" t="n"/>
       <c r="Y138" s="15" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" hidden="1" outlineLevel="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10261,7 +10273,7 @@
       <c r="X139" s="15" t="n"/>
       <c r="Y139" s="15" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" hidden="1" outlineLevel="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10395,7 +10407,7 @@
       <c r="X141" s="15" t="n"/>
       <c r="Y141" s="15" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" hidden="1" outlineLevel="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10464,7 +10476,7 @@
       <c r="X142" s="15" t="n"/>
       <c r="Y142" s="15" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" hidden="1" outlineLevel="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10533,7 +10545,7 @@
       <c r="X143" s="15" t="n"/>
       <c r="Y143" s="15" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" hidden="1" outlineLevel="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10602,7 +10614,7 @@
       <c r="X144" s="15" t="n"/>
       <c r="Y144" s="15" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" hidden="1" outlineLevel="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10671,7 +10683,7 @@
       <c r="X145" s="15" t="n"/>
       <c r="Y145" s="15" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" hidden="1" outlineLevel="1">
       <c r="A146" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10740,7 +10752,7 @@
       <c r="X146" s="15" t="n"/>
       <c r="Y146" s="15" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" hidden="1" outlineLevel="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10809,7 +10821,7 @@
       <c r="X147" s="15" t="n"/>
       <c r="Y147" s="15" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" hidden="1" outlineLevel="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -10943,7 +10955,7 @@
       <c r="X149" s="15" t="n"/>
       <c r="Y149" s="15" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" hidden="1" outlineLevel="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11008,7 +11020,7 @@
       <c r="X150" s="15" t="n"/>
       <c r="Y150" s="15" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" hidden="1" outlineLevel="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11073,7 +11085,7 @@
       <c r="X151" s="15" t="n"/>
       <c r="Y151" s="15" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" hidden="1" outlineLevel="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11138,7 +11150,7 @@
       <c r="X152" s="15" t="n"/>
       <c r="Y152" s="15" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" hidden="1" outlineLevel="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11203,7 +11215,7 @@
       <c r="X153" s="15" t="n"/>
       <c r="Y153" s="15" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" hidden="1" outlineLevel="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11333,7 +11345,7 @@
       <c r="X155" s="15" t="n"/>
       <c r="Y155" s="15" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" hidden="1" outlineLevel="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11398,7 +11410,7 @@
       <c r="X156" s="15" t="n"/>
       <c r="Y156" s="15" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" hidden="1" outlineLevel="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11463,7 +11475,7 @@
       <c r="X157" s="15" t="n"/>
       <c r="Y157" s="15" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" hidden="1" outlineLevel="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11528,7 +11540,7 @@
       <c r="X158" s="15" t="n"/>
       <c r="Y158" s="15" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" hidden="1" outlineLevel="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11662,7 +11674,7 @@
       <c r="X160" s="15" t="n"/>
       <c r="Y160" s="15" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" hidden="1" outlineLevel="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11731,7 +11743,7 @@
       <c r="X161" s="15" t="n"/>
       <c r="Y161" s="15" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" hidden="1" outlineLevel="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11800,7 +11812,7 @@
       <c r="X162" s="15" t="n"/>
       <c r="Y162" s="15" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" hidden="1" outlineLevel="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11869,7 +11881,7 @@
       <c r="X163" s="15" t="n"/>
       <c r="Y163" s="15" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" hidden="1" outlineLevel="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -11938,7 +11950,7 @@
       <c r="X164" s="15" t="n"/>
       <c r="Y164" s="15" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" hidden="1" outlineLevel="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12007,7 +12019,7 @@
       <c r="X165" s="15" t="n"/>
       <c r="Y165" s="15" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" hidden="1" outlineLevel="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12141,7 +12153,7 @@
       <c r="X167" s="15" t="n"/>
       <c r="Y167" s="15" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" hidden="1" outlineLevel="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12206,7 +12218,7 @@
       <c r="X168" s="15" t="n"/>
       <c r="Y168" s="15" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" hidden="1" outlineLevel="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12271,7 +12283,7 @@
       <c r="X169" s="15" t="n"/>
       <c r="Y169" s="15" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" hidden="1" outlineLevel="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12336,7 +12348,7 @@
       <c r="X170" s="15" t="n"/>
       <c r="Y170" s="15" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" hidden="1" outlineLevel="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12466,7 +12478,7 @@
       <c r="X172" s="15" t="n"/>
       <c r="Y172" s="15" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" hidden="1" outlineLevel="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12531,7 +12543,7 @@
       <c r="X173" s="15" t="n"/>
       <c r="Y173" s="15" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" hidden="1" outlineLevel="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12596,7 +12608,7 @@
       <c r="X174" s="15" t="n"/>
       <c r="Y174" s="15" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" hidden="1" outlineLevel="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12661,7 +12673,7 @@
       <c r="X175" s="15" t="n"/>
       <c r="Y175" s="15" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" hidden="1" outlineLevel="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12726,7 +12738,7 @@
       <c r="X176" s="15" t="n"/>
       <c r="Y176" s="15" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" hidden="1" outlineLevel="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12791,7 +12803,7 @@
       <c r="X177" s="15" t="n"/>
       <c r="Y177" s="15" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" hidden="1" outlineLevel="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -12986,7 +12998,7 @@
       <c r="X180" s="15" t="n"/>
       <c r="Y180" s="15" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" hidden="1" outlineLevel="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13051,7 +13063,7 @@
       <c r="X181" s="15" t="n"/>
       <c r="Y181" s="15" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" hidden="1" outlineLevel="1">
       <c r="A182" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13116,7 +13128,7 @@
       <c r="X182" s="15" t="n"/>
       <c r="Y182" s="15" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" hidden="1" outlineLevel="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13250,7 +13262,7 @@
       <c r="X184" s="15" t="n"/>
       <c r="Y184" s="15" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" hidden="1" outlineLevel="1">
       <c r="A185" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13319,7 +13331,7 @@
       <c r="X185" s="15" t="n"/>
       <c r="Y185" s="15" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" hidden="1" outlineLevel="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13388,7 +13400,7 @@
       <c r="X186" s="15" t="n"/>
       <c r="Y186" s="15" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" hidden="1" outlineLevel="1">
       <c r="A187" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13457,7 +13469,7 @@
       <c r="X187" s="15" t="n"/>
       <c r="Y187" s="15" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" hidden="1" outlineLevel="1">
       <c r="A188" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13591,7 +13603,7 @@
       <c r="X189" s="15" t="n"/>
       <c r="Y189" s="15" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" hidden="1" outlineLevel="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13656,7 +13668,7 @@
       <c r="X190" s="15" t="n"/>
       <c r="Y190" s="15" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" hidden="1" outlineLevel="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13786,7 +13798,7 @@
       <c r="X192" s="15" t="n"/>
       <c r="Y192" s="15" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" hidden="1" outlineLevel="1">
       <c r="A193" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13851,7 +13863,7 @@
       <c r="X193" s="15" t="n"/>
       <c r="Y193" s="15" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" hidden="1" outlineLevel="1">
       <c r="A194" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13916,7 +13928,7 @@
       <c r="X194" s="15" t="n"/>
       <c r="Y194" s="15" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" hidden="1" outlineLevel="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -13981,7 +13993,7 @@
       <c r="X195" s="15" t="n"/>
       <c r="Y195" s="15" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" hidden="1" outlineLevel="1">
       <c r="A196" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14046,7 +14058,7 @@
       <c r="X196" s="15" t="n"/>
       <c r="Y196" s="15" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" hidden="1" outlineLevel="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14111,7 +14123,7 @@
       <c r="X197" s="15" t="n"/>
       <c r="Y197" s="15" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" hidden="1" outlineLevel="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14245,7 +14257,7 @@
       <c r="X199" s="15" t="n"/>
       <c r="Y199" s="15" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" hidden="1" outlineLevel="1">
       <c r="A200" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14314,7 +14326,7 @@
       <c r="X200" s="15" t="n"/>
       <c r="Y200" s="15" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" hidden="1" outlineLevel="1">
       <c r="A201" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14383,7 +14395,7 @@
       <c r="X201" s="15" t="n"/>
       <c r="Y201" s="15" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" hidden="1" outlineLevel="1">
       <c r="A202" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14452,7 +14464,7 @@
       <c r="X202" s="15" t="n"/>
       <c r="Y202" s="15" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" hidden="1" outlineLevel="1">
       <c r="A203" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14586,7 +14598,7 @@
       <c r="X204" s="15" t="n"/>
       <c r="Y204" s="15" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" hidden="1" outlineLevel="1">
       <c r="A205" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14651,7 +14663,7 @@
       <c r="X205" s="15" t="n"/>
       <c r="Y205" s="15" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" hidden="1" outlineLevel="1">
       <c r="A206" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14716,7 +14728,7 @@
       <c r="X206" s="15" t="n"/>
       <c r="Y206" s="15" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" hidden="1" outlineLevel="1">
       <c r="A207" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14781,7 +14793,7 @@
       <c r="X207" s="15" t="n"/>
       <c r="Y207" s="15" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" hidden="1" outlineLevel="1">
       <c r="A208" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14846,7 +14858,7 @@
       <c r="X208" s="15" t="n"/>
       <c r="Y208" s="15" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" hidden="1" outlineLevel="1">
       <c r="A209" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -14911,7 +14923,7 @@
       <c r="X209" s="15" t="n"/>
       <c r="Y209" s="15" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" hidden="1" outlineLevel="1">
       <c r="A210" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15041,7 +15053,7 @@
       <c r="X211" s="15" t="n"/>
       <c r="Y211" s="15" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" hidden="1" outlineLevel="1">
       <c r="A212" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15106,7 +15118,7 @@
       <c r="X212" s="15" t="n"/>
       <c r="Y212" s="15" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" hidden="1" outlineLevel="1">
       <c r="A213" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15171,7 +15183,7 @@
       <c r="X213" s="15" t="n"/>
       <c r="Y213" s="15" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" hidden="1" outlineLevel="1">
       <c r="A214" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15301,7 +15313,7 @@
       <c r="X215" s="15" t="n"/>
       <c r="Y215" s="15" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" hidden="1" outlineLevel="1">
       <c r="A216" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15366,7 +15378,7 @@
       <c r="X216" s="15" t="n"/>
       <c r="Y216" s="15" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" hidden="1" outlineLevel="1">
       <c r="A217" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15496,7 +15508,7 @@
       <c r="X218" s="15" t="n"/>
       <c r="Y218" s="15" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" hidden="1" outlineLevel="1">
       <c r="A219" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15626,7 +15638,7 @@
       <c r="X220" s="15" t="n"/>
       <c r="Y220" s="15" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" hidden="1" outlineLevel="1">
       <c r="A221" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15691,7 +15703,7 @@
       <c r="X221" s="15" t="n"/>
       <c r="Y221" s="15" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" hidden="1" outlineLevel="1">
       <c r="A222" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -15886,7 +15898,7 @@
       <c r="X224" s="15" t="n"/>
       <c r="Y224" s="15" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" hidden="1" outlineLevel="1">
       <c r="A225" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16085,7 +16097,7 @@
       <c r="X227" s="15" t="n"/>
       <c r="Y227" s="15" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" hidden="1" outlineLevel="1">
       <c r="A228" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16219,7 +16231,7 @@
       <c r="X229" s="15" t="n"/>
       <c r="Y229" s="15" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" hidden="1" outlineLevel="1">
       <c r="A230" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16284,7 +16296,7 @@
       <c r="X230" s="15" t="n"/>
       <c r="Y230" s="15" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" hidden="1" outlineLevel="1">
       <c r="A231" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16414,7 +16426,7 @@
       <c r="X232" s="15" t="n"/>
       <c r="Y232" s="15" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" hidden="1" outlineLevel="1">
       <c r="A233" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16479,7 +16491,7 @@
       <c r="X233" s="15" t="n"/>
       <c r="Y233" s="15" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" hidden="1" outlineLevel="1">
       <c r="A234" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16544,7 +16556,7 @@
       <c r="X234" s="15" t="n"/>
       <c r="Y234" s="15" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" hidden="1" outlineLevel="1">
       <c r="A235" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16674,7 +16686,7 @@
       <c r="X236" s="15" t="n"/>
       <c r="Y236" s="15" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" hidden="1" outlineLevel="1">
       <c r="A237" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16739,7 +16751,7 @@
       <c r="X237" s="15" t="n"/>
       <c r="Y237" s="15" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" hidden="1" outlineLevel="1">
       <c r="A238" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16804,7 +16816,7 @@
       <c r="X238" s="15" t="n"/>
       <c r="Y238" s="15" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" hidden="1" outlineLevel="1">
       <c r="A239" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -16934,7 +16946,7 @@
       <c r="X240" s="15" t="n"/>
       <c r="Y240" s="15" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" hidden="1" outlineLevel="1">
       <c r="A241" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -17064,7 +17076,7 @@
       <c r="X242" s="15" t="n"/>
       <c r="Y242" s="15" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" hidden="1" outlineLevel="1">
       <c r="A243" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -17198,7 +17210,7 @@
       <c r="X244" s="15" t="n"/>
       <c r="Y244" s="15" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" hidden="1" outlineLevel="1">
       <c r="A245" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -17267,7 +17279,7 @@
       <c r="X245" s="15" t="n"/>
       <c r="Y245" s="15" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" hidden="1" outlineLevel="1">
       <c r="A246" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -17336,7 +17348,7 @@
       <c r="X246" s="15" t="n"/>
       <c r="Y246" s="15" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" hidden="1" outlineLevel="1">
       <c r="A247" s="9" t="inlineStr">
         <is>
           <t>P1</t>
@@ -17466,7 +17478,7 @@
       <c r="X248" s="15" t="n"/>
       <c r="Y248" s="15" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" hidden="1" outlineLevel="1">
       <c r="A249" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17527,7 +17539,7 @@
       <c r="X249" s="15" t="n"/>
       <c r="Y249" s="15" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" hidden="1" outlineLevel="1">
       <c r="A250" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17588,7 +17600,7 @@
       <c r="X250" s="15" t="n"/>
       <c r="Y250" s="15" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" hidden="1" outlineLevel="1">
       <c r="A251" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17649,7 +17661,7 @@
       <c r="X251" s="15" t="n"/>
       <c r="Y251" s="15" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" hidden="1" outlineLevel="1">
       <c r="A252" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17710,7 +17722,7 @@
       <c r="X252" s="15" t="n"/>
       <c r="Y252" s="15" t="n"/>
     </row>
-    <row r="253">
+    <row r="253" hidden="1" outlineLevel="1">
       <c r="A253" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17836,7 +17848,7 @@
       <c r="X254" s="15" t="n"/>
       <c r="Y254" s="15" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" hidden="1" outlineLevel="1">
       <c r="A255" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17901,7 +17913,7 @@
       <c r="X255" s="15" t="n"/>
       <c r="Y255" s="15" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" hidden="1" outlineLevel="1">
       <c r="A256" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -17966,7 +17978,7 @@
       <c r="X256" s="15" t="n"/>
       <c r="Y256" s="15" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" hidden="1" outlineLevel="1">
       <c r="A257" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18031,7 +18043,7 @@
       <c r="X257" s="15" t="n"/>
       <c r="Y257" s="15" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" hidden="1" outlineLevel="1">
       <c r="A258" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18096,7 +18108,7 @@
       <c r="X258" s="15" t="n"/>
       <c r="Y258" s="15" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" hidden="1" outlineLevel="1">
       <c r="A259" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18161,7 +18173,7 @@
       <c r="X259" s="15" t="n"/>
       <c r="Y259" s="15" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" hidden="1" outlineLevel="1">
       <c r="A260" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18291,7 +18303,7 @@
       <c r="X261" s="15" t="n"/>
       <c r="Y261" s="15" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" hidden="1" outlineLevel="1">
       <c r="A262" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18356,7 +18368,7 @@
       <c r="X262" s="15" t="n"/>
       <c r="Y262" s="15" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" hidden="1" outlineLevel="1">
       <c r="A263" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18421,7 +18433,7 @@
       <c r="X263" s="15" t="n"/>
       <c r="Y263" s="15" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" hidden="1" outlineLevel="1">
       <c r="A264" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18555,7 +18567,7 @@
       <c r="X265" s="15" t="n"/>
       <c r="Y265" s="15" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" hidden="1" outlineLevel="1">
       <c r="A266" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18624,7 +18636,7 @@
       <c r="X266" s="15" t="n"/>
       <c r="Y266" s="15" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" hidden="1" outlineLevel="1">
       <c r="A267" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18693,7 +18705,7 @@
       <c r="X267" s="15" t="n"/>
       <c r="Y267" s="15" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" hidden="1" outlineLevel="1">
       <c r="A268" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18762,7 +18774,7 @@
       <c r="X268" s="15" t="n"/>
       <c r="Y268" s="15" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" hidden="1" outlineLevel="1">
       <c r="A269" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18831,7 +18843,7 @@
       <c r="X269" s="15" t="n"/>
       <c r="Y269" s="15" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" hidden="1" outlineLevel="1">
       <c r="A270" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -18965,7 +18977,7 @@
       <c r="X271" s="15" t="n"/>
       <c r="Y271" s="15" t="n"/>
     </row>
-    <row r="272">
+    <row r="272" hidden="1" outlineLevel="1">
       <c r="A272" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19099,7 +19111,7 @@
       <c r="X273" s="15" t="n"/>
       <c r="Y273" s="15" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" hidden="1" outlineLevel="1">
       <c r="A274" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19168,7 +19180,7 @@
       <c r="X274" s="15" t="n"/>
       <c r="Y274" s="15" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" hidden="1" outlineLevel="1">
       <c r="A275" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19237,7 +19249,7 @@
       <c r="X275" s="15" t="n"/>
       <c r="Y275" s="15" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" hidden="1" outlineLevel="1">
       <c r="A276" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19306,7 +19318,7 @@
       <c r="X276" s="15" t="n"/>
       <c r="Y276" s="15" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" hidden="1" outlineLevel="1">
       <c r="A277" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19444,7 +19456,7 @@
       <c r="X278" s="15" t="n"/>
       <c r="Y278" s="15" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" hidden="1" outlineLevel="1">
       <c r="A279" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19513,7 +19525,7 @@
       <c r="X279" s="15" t="n"/>
       <c r="Y279" s="15" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" hidden="1" outlineLevel="1">
       <c r="A280" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19647,7 +19659,7 @@
       <c r="X281" s="15" t="n"/>
       <c r="Y281" s="15" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" hidden="1" outlineLevel="1">
       <c r="A282" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19712,7 +19724,7 @@
       <c r="X282" s="15" t="n"/>
       <c r="Y282" s="15" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" hidden="1" outlineLevel="1">
       <c r="A283" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19842,7 +19854,7 @@
       <c r="X284" s="15" t="n"/>
       <c r="Y284" s="15" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" hidden="1" outlineLevel="1">
       <c r="A285" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -19972,7 +19984,7 @@
       <c r="X286" s="15" t="n"/>
       <c r="Y286" s="15" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" hidden="1" outlineLevel="1">
       <c r="A287" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20037,7 +20049,7 @@
       <c r="X287" s="15" t="n"/>
       <c r="Y287" s="15" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" hidden="1" outlineLevel="1">
       <c r="A288" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20102,7 +20114,7 @@
       <c r="X288" s="15" t="n"/>
       <c r="Y288" s="15" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" hidden="1" outlineLevel="1">
       <c r="A289" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20167,7 +20179,7 @@
       <c r="X289" s="15" t="n"/>
       <c r="Y289" s="15" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" hidden="1" outlineLevel="1">
       <c r="A290" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20297,7 +20309,7 @@
       <c r="X291" s="15" t="n"/>
       <c r="Y291" s="15" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" hidden="1" outlineLevel="1">
       <c r="A292" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20362,7 +20374,7 @@
       <c r="X292" s="15" t="n"/>
       <c r="Y292" s="15" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" hidden="1" outlineLevel="1">
       <c r="A293" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20427,7 +20439,7 @@
       <c r="X293" s="15" t="n"/>
       <c r="Y293" s="15" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" hidden="1" outlineLevel="1">
       <c r="A294" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20492,7 +20504,7 @@
       <c r="X294" s="15" t="n"/>
       <c r="Y294" s="15" t="n"/>
     </row>
-    <row r="295">
+    <row r="295" hidden="1" outlineLevel="1">
       <c r="A295" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20557,7 +20569,7 @@
       <c r="X295" s="15" t="n"/>
       <c r="Y295" s="15" t="n"/>
     </row>
-    <row r="296">
+    <row r="296" hidden="1" outlineLevel="1">
       <c r="A296" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20622,7 +20634,7 @@
       <c r="X296" s="15" t="n"/>
       <c r="Y296" s="15" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" hidden="1" outlineLevel="1">
       <c r="A297" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20752,7 +20764,7 @@
       <c r="X298" s="15" t="n"/>
       <c r="Y298" s="15" t="n"/>
     </row>
-    <row r="299">
+    <row r="299" hidden="1" outlineLevel="1">
       <c r="A299" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20817,7 +20829,7 @@
       <c r="X299" s="15" t="n"/>
       <c r="Y299" s="15" t="n"/>
     </row>
-    <row r="300">
+    <row r="300" hidden="1" outlineLevel="1">
       <c r="A300" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -20947,7 +20959,7 @@
       <c r="X301" s="15" t="n"/>
       <c r="Y301" s="15" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" hidden="1" outlineLevel="1">
       <c r="A302" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21077,7 +21089,7 @@
       <c r="X303" s="15" t="n"/>
       <c r="Y303" s="15" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" hidden="1" outlineLevel="1">
       <c r="A304" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21211,7 +21223,7 @@
       <c r="X305" s="15" t="n"/>
       <c r="Y305" s="15" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" hidden="1" outlineLevel="1">
       <c r="A306" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21280,7 +21292,7 @@
       <c r="X306" s="15" t="n"/>
       <c r="Y306" s="15" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" hidden="1" outlineLevel="1">
       <c r="A307" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21349,7 +21361,7 @@
       <c r="X307" s="15" t="n"/>
       <c r="Y307" s="15" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" hidden="1" outlineLevel="1">
       <c r="A308" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21418,7 +21430,7 @@
       <c r="X308" s="15" t="n"/>
       <c r="Y308" s="15" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" hidden="1" outlineLevel="1">
       <c r="A309" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21552,7 +21564,7 @@
       <c r="X310" s="15" t="n"/>
       <c r="Y310" s="15" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" hidden="1" outlineLevel="1">
       <c r="A311" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21617,7 +21629,7 @@
       <c r="X311" s="15" t="n"/>
       <c r="Y311" s="15" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" hidden="1" outlineLevel="1">
       <c r="A312" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21682,7 +21694,7 @@
       <c r="X312" s="15" t="n"/>
       <c r="Y312" s="15" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" hidden="1" outlineLevel="1">
       <c r="A313" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21747,7 +21759,7 @@
       <c r="X313" s="15" t="n"/>
       <c r="Y313" s="15" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" hidden="1" outlineLevel="1">
       <c r="A314" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21812,7 +21824,7 @@
       <c r="X314" s="15" t="n"/>
       <c r="Y314" s="15" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" hidden="1" outlineLevel="1">
       <c r="A315" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -21877,7 +21889,7 @@
       <c r="X315" s="15" t="n"/>
       <c r="Y315" s="15" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" hidden="1" outlineLevel="1">
       <c r="A316" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22011,7 +22023,7 @@
       <c r="X317" s="15" t="n"/>
       <c r="Y317" s="15" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" hidden="1" outlineLevel="1">
       <c r="A318" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22080,7 +22092,7 @@
       <c r="X318" s="15" t="n"/>
       <c r="Y318" s="15" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" hidden="1" outlineLevel="1">
       <c r="A319" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22214,7 +22226,7 @@
       <c r="X320" s="15" t="n"/>
       <c r="Y320" s="15" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" hidden="1" outlineLevel="1">
       <c r="A321" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22279,7 +22291,7 @@
       <c r="X321" s="15" t="n"/>
       <c r="Y321" s="15" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" hidden="1" outlineLevel="1">
       <c r="A322" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22344,7 +22356,7 @@
       <c r="X322" s="15" t="n"/>
       <c r="Y322" s="15" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" hidden="1" outlineLevel="1">
       <c r="A323" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22409,7 +22421,7 @@
       <c r="X323" s="15" t="n"/>
       <c r="Y323" s="15" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" hidden="1" outlineLevel="1">
       <c r="A324" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22474,7 +22486,7 @@
       <c r="X324" s="15" t="n"/>
       <c r="Y324" s="15" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" hidden="1" outlineLevel="1">
       <c r="A325" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22669,7 +22681,7 @@
       <c r="X327" s="15" t="n"/>
       <c r="Y327" s="15" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" hidden="1" outlineLevel="1">
       <c r="A328" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22734,7 +22746,7 @@
       <c r="X328" s="15" t="n"/>
       <c r="Y328" s="15" t="n"/>
     </row>
-    <row r="329">
+    <row r="329" hidden="1" outlineLevel="1">
       <c r="A329" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22799,7 +22811,7 @@
       <c r="X329" s="15" t="n"/>
       <c r="Y329" s="15" t="n"/>
     </row>
-    <row r="330">
+    <row r="330" hidden="1" outlineLevel="1">
       <c r="A330" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22929,7 +22941,7 @@
       <c r="X331" s="15" t="n"/>
       <c r="Y331" s="15" t="n"/>
     </row>
-    <row r="332">
+    <row r="332" hidden="1" outlineLevel="1">
       <c r="A332" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -22994,7 +23006,7 @@
       <c r="X332" s="15" t="n"/>
       <c r="Y332" s="15" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" hidden="1" outlineLevel="1">
       <c r="A333" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23128,7 +23140,7 @@
       <c r="X334" s="15" t="n"/>
       <c r="Y334" s="15" t="n"/>
     </row>
-    <row r="335">
+    <row r="335" hidden="1" outlineLevel="1">
       <c r="A335" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23262,7 +23274,7 @@
       <c r="X336" s="15" t="n"/>
       <c r="Y336" s="15" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" hidden="1" outlineLevel="1">
       <c r="A337" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23327,7 +23339,7 @@
       <c r="X337" s="15" t="n"/>
       <c r="Y337" s="15" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" hidden="1" outlineLevel="1">
       <c r="A338" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23392,7 +23404,7 @@
       <c r="X338" s="15" t="n"/>
       <c r="Y338" s="15" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" hidden="1" outlineLevel="1">
       <c r="A339" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23526,7 +23538,7 @@
       <c r="X340" s="15" t="n"/>
       <c r="Y340" s="15" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" hidden="1" outlineLevel="1">
       <c r="A341" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23595,7 +23607,7 @@
       <c r="X341" s="15" t="n"/>
       <c r="Y341" s="15" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" hidden="1" outlineLevel="1">
       <c r="A342" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23729,7 +23741,7 @@
       <c r="X343" s="15" t="n"/>
       <c r="Y343" s="15" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" hidden="1" outlineLevel="1">
       <c r="A344" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23794,7 +23806,7 @@
       <c r="X344" s="15" t="n"/>
       <c r="Y344" s="15" t="n"/>
     </row>
-    <row r="345">
+    <row r="345" hidden="1" outlineLevel="1">
       <c r="A345" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23859,7 +23871,7 @@
       <c r="X345" s="15" t="n"/>
       <c r="Y345" s="15" t="n"/>
     </row>
-    <row r="346">
+    <row r="346" hidden="1" outlineLevel="1">
       <c r="A346" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -23989,7 +24001,7 @@
       <c r="X347" s="15" t="n"/>
       <c r="Y347" s="15" t="n"/>
     </row>
-    <row r="348">
+    <row r="348" hidden="1" outlineLevel="1">
       <c r="A348" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24054,7 +24066,7 @@
       <c r="X348" s="15" t="n"/>
       <c r="Y348" s="15" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" hidden="1" outlineLevel="1">
       <c r="A349" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24184,7 +24196,7 @@
       <c r="X350" s="15" t="n"/>
       <c r="Y350" s="15" t="n"/>
     </row>
-    <row r="351">
+    <row r="351" hidden="1" outlineLevel="1">
       <c r="A351" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24310,7 +24322,7 @@
       <c r="X352" s="15" t="n"/>
       <c r="Y352" s="15" t="n"/>
     </row>
-    <row r="353">
+    <row r="353" hidden="1" outlineLevel="1">
       <c r="A353" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24371,7 +24383,7 @@
       <c r="X353" s="15" t="n"/>
       <c r="Y353" s="15" t="n"/>
     </row>
-    <row r="354">
+    <row r="354" hidden="1" outlineLevel="1">
       <c r="A354" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24566,7 +24578,7 @@
       <c r="X356" s="15" t="n"/>
       <c r="Y356" s="15" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" hidden="1" outlineLevel="1">
       <c r="A357" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24631,7 +24643,7 @@
       <c r="X357" s="15" t="n"/>
       <c r="Y357" s="15" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" hidden="1" outlineLevel="1">
       <c r="A358" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24696,7 +24708,7 @@
       <c r="X358" s="15" t="n"/>
       <c r="Y358" s="15" t="n"/>
     </row>
-    <row r="359">
+    <row r="359" hidden="1" outlineLevel="1">
       <c r="A359" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24826,7 +24838,7 @@
       <c r="X360" s="15" t="n"/>
       <c r="Y360" s="15" t="n"/>
     </row>
-    <row r="361">
+    <row r="361" hidden="1" outlineLevel="1">
       <c r="A361" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -24956,7 +24968,7 @@
       <c r="X362" s="15" t="n"/>
       <c r="Y362" s="15" t="n"/>
     </row>
-    <row r="363">
+    <row r="363" hidden="1" outlineLevel="1">
       <c r="A363" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25021,7 +25033,7 @@
       <c r="X363" s="15" t="n"/>
       <c r="Y363" s="15" t="n"/>
     </row>
-    <row r="364">
+    <row r="364" hidden="1" outlineLevel="1">
       <c r="A364" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25086,7 +25098,7 @@
       <c r="X364" s="15" t="n"/>
       <c r="Y364" s="15" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" hidden="1" outlineLevel="1">
       <c r="A365" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25151,7 +25163,7 @@
       <c r="X365" s="15" t="n"/>
       <c r="Y365" s="15" t="n"/>
     </row>
-    <row r="366">
+    <row r="366" hidden="1" outlineLevel="1">
       <c r="A366" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25216,7 +25228,7 @@
       <c r="X366" s="15" t="n"/>
       <c r="Y366" s="15" t="n"/>
     </row>
-    <row r="367">
+    <row r="367" hidden="1" outlineLevel="1">
       <c r="A367" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25346,7 +25358,7 @@
       <c r="X368" s="15" t="n"/>
       <c r="Y368" s="15" t="n"/>
     </row>
-    <row r="369">
+    <row r="369" hidden="1" outlineLevel="1">
       <c r="A369" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25411,7 +25423,7 @@
       <c r="X369" s="15" t="n"/>
       <c r="Y369" s="15" t="n"/>
     </row>
-    <row r="370">
+    <row r="370" hidden="1" outlineLevel="1">
       <c r="A370" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25537,7 +25549,7 @@
       <c r="X371" s="15" t="n"/>
       <c r="Y371" s="15" t="n"/>
     </row>
-    <row r="372">
+    <row r="372" hidden="1" outlineLevel="1">
       <c r="A372" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25598,7 +25610,7 @@
       <c r="X372" s="15" t="n"/>
       <c r="Y372" s="15" t="n"/>
     </row>
-    <row r="373">
+    <row r="373" hidden="1" outlineLevel="1">
       <c r="A373" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25793,7 +25805,7 @@
       <c r="X375" s="15" t="n"/>
       <c r="Y375" s="15" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" hidden="1" outlineLevel="1">
       <c r="A376" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -25927,7 +25939,7 @@
       <c r="X377" s="15" t="n"/>
       <c r="Y377" s="15" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" hidden="1" outlineLevel="1">
       <c r="A378" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26057,7 +26069,7 @@
       <c r="X379" s="15" t="n"/>
       <c r="Y379" s="15" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" hidden="1" outlineLevel="1">
       <c r="A380" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26191,7 +26203,7 @@
       <c r="X381" s="15" t="n"/>
       <c r="Y381" s="15" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" hidden="1" outlineLevel="1">
       <c r="A382" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26260,7 +26272,7 @@
       <c r="X382" s="15" t="n"/>
       <c r="Y382" s="15" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" hidden="1" outlineLevel="1">
       <c r="A383" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26329,7 +26341,7 @@
       <c r="X383" s="15" t="n"/>
       <c r="Y383" s="15" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" hidden="1" outlineLevel="1">
       <c r="A384" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26463,7 +26475,7 @@
       <c r="X385" s="15" t="n"/>
       <c r="Y385" s="15" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" hidden="1" outlineLevel="1">
       <c r="A386" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26528,7 +26540,7 @@
       <c r="X386" s="15" t="n"/>
       <c r="Y386" s="15" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" hidden="1" outlineLevel="1">
       <c r="A387" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26662,7 +26674,7 @@
       <c r="X388" s="15" t="n"/>
       <c r="Y388" s="15" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" hidden="1" outlineLevel="1">
       <c r="A389" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26731,7 +26743,7 @@
       <c r="X389" s="15" t="n"/>
       <c r="Y389" s="15" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" hidden="1" outlineLevel="1">
       <c r="A390" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26865,7 +26877,7 @@
       <c r="X391" s="15" t="n"/>
       <c r="Y391" s="15" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" hidden="1" outlineLevel="1">
       <c r="A392" s="10" t="inlineStr">
         <is>
           <t>P2</t>
@@ -26999,7 +27011,7 @@
       <c r="X393" s="15" t="n"/>
       <c r="Y393" s="15" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" hidden="1" outlineLevel="1">
       <c r="A394" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27068,7 +27080,7 @@
       <c r="X394" s="15" t="n"/>
       <c r="Y394" s="15" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" hidden="1" outlineLevel="1">
       <c r="A395" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27137,7 +27149,7 @@
       <c r="X395" s="15" t="n"/>
       <c r="Y395" s="15" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" hidden="1" outlineLevel="1">
       <c r="A396" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27206,7 +27218,7 @@
       <c r="X396" s="15" t="n"/>
       <c r="Y396" s="15" t="n"/>
     </row>
-    <row r="397">
+    <row r="397" hidden="1" outlineLevel="1">
       <c r="A397" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27344,7 +27356,7 @@
       <c r="X398" s="15" t="n"/>
       <c r="Y398" s="15" t="n"/>
     </row>
-    <row r="399">
+    <row r="399" hidden="1" outlineLevel="1">
       <c r="A399" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27413,7 +27425,7 @@
       <c r="X399" s="15" t="n"/>
       <c r="Y399" s="15" t="n"/>
     </row>
-    <row r="400">
+    <row r="400" hidden="1" outlineLevel="1">
       <c r="A400" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27547,7 +27559,7 @@
       <c r="X401" s="15" t="n"/>
       <c r="Y401" s="15" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" hidden="1" outlineLevel="1">
       <c r="A402" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27612,7 +27624,7 @@
       <c r="X402" s="15" t="n"/>
       <c r="Y402" s="15" t="n"/>
     </row>
-    <row r="403">
+    <row r="403" hidden="1" outlineLevel="1">
       <c r="A403" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27677,7 +27689,7 @@
       <c r="X403" s="15" t="n"/>
       <c r="Y403" s="15" t="n"/>
     </row>
-    <row r="404">
+    <row r="404" hidden="1" outlineLevel="1">
       <c r="A404" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27742,7 +27754,7 @@
       <c r="X404" s="15" t="n"/>
       <c r="Y404" s="15" t="n"/>
     </row>
-    <row r="405">
+    <row r="405" hidden="1" outlineLevel="1">
       <c r="A405" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27807,7 +27819,7 @@
       <c r="X405" s="15" t="n"/>
       <c r="Y405" s="15" t="n"/>
     </row>
-    <row r="406">
+    <row r="406" hidden="1" outlineLevel="1">
       <c r="A406" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -27937,7 +27949,7 @@
       <c r="X407" s="15" t="n"/>
       <c r="Y407" s="15" t="n"/>
     </row>
-    <row r="408">
+    <row r="408" hidden="1" outlineLevel="1">
       <c r="A408" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28002,7 +28014,7 @@
       <c r="X408" s="15" t="n"/>
       <c r="Y408" s="15" t="n"/>
     </row>
-    <row r="409">
+    <row r="409" hidden="1" outlineLevel="1">
       <c r="A409" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28132,7 +28144,7 @@
       <c r="X410" s="15" t="n"/>
       <c r="Y410" s="15" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" hidden="1" outlineLevel="1">
       <c r="A411" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28327,7 +28339,7 @@
       <c r="X413" s="15" t="n"/>
       <c r="Y413" s="15" t="n"/>
     </row>
-    <row r="414">
+    <row r="414" hidden="1" outlineLevel="1">
       <c r="A414" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28457,7 +28469,7 @@
       <c r="X415" s="15" t="n"/>
       <c r="Y415" s="15" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" hidden="1" outlineLevel="1">
       <c r="A416" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28587,7 +28599,7 @@
       <c r="X417" s="15" t="n"/>
       <c r="Y417" s="15" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" hidden="1" outlineLevel="1">
       <c r="A418" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28652,7 +28664,7 @@
       <c r="X418" s="15" t="n"/>
       <c r="Y418" s="15" t="n"/>
     </row>
-    <row r="419">
+    <row r="419" hidden="1" outlineLevel="1">
       <c r="A419" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28782,7 +28794,7 @@
       <c r="X420" s="15" t="n"/>
       <c r="Y420" s="15" t="n"/>
     </row>
-    <row r="421">
+    <row r="421" hidden="1" outlineLevel="1">
       <c r="A421" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -28981,7 +28993,7 @@
       <c r="X423" s="15" t="n"/>
       <c r="Y423" s="15" t="n"/>
     </row>
-    <row r="424">
+    <row r="424" hidden="1" outlineLevel="1">
       <c r="A424" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29115,7 +29127,7 @@
       <c r="X425" s="15" t="n"/>
       <c r="Y425" s="15" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" hidden="1" outlineLevel="1">
       <c r="A426" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29180,7 +29192,7 @@
       <c r="X426" s="15" t="n"/>
       <c r="Y426" s="15" t="n"/>
     </row>
-    <row r="427">
+    <row r="427" hidden="1" outlineLevel="1">
       <c r="A427" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29310,7 +29322,7 @@
       <c r="X428" s="15" t="n"/>
       <c r="Y428" s="15" t="n"/>
     </row>
-    <row r="429">
+    <row r="429" hidden="1" outlineLevel="1">
       <c r="A429" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29375,7 +29387,7 @@
       <c r="X429" s="15" t="n"/>
       <c r="Y429" s="15" t="n"/>
     </row>
-    <row r="430">
+    <row r="430" hidden="1" outlineLevel="1">
       <c r="A430" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29505,7 +29517,7 @@
       <c r="X431" s="15" t="n"/>
       <c r="Y431" s="15" t="n"/>
     </row>
-    <row r="432">
+    <row r="432" hidden="1" outlineLevel="1">
       <c r="A432" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29570,7 +29582,7 @@
       <c r="X432" s="15" t="n"/>
       <c r="Y432" s="15" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" hidden="1" outlineLevel="1">
       <c r="A433" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29700,7 +29712,7 @@
       <c r="X434" s="15" t="n"/>
       <c r="Y434" s="15" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" hidden="1" outlineLevel="1">
       <c r="A435" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29834,7 +29846,7 @@
       <c r="X436" s="15" t="n"/>
       <c r="Y436" s="15" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" hidden="1" outlineLevel="1">
       <c r="A437" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -29903,7 +29915,7 @@
       <c r="X437" s="15" t="n"/>
       <c r="Y437" s="15" t="n"/>
     </row>
-    <row r="438">
+    <row r="438" hidden="1" outlineLevel="1">
       <c r="A438" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30037,7 +30049,7 @@
       <c r="X439" s="15" t="n"/>
       <c r="Y439" s="15" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" hidden="1" outlineLevel="1">
       <c r="A440" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30102,7 +30114,7 @@
       <c r="X440" s="15" t="n"/>
       <c r="Y440" s="15" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" hidden="1" outlineLevel="1">
       <c r="A441" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30232,7 +30244,7 @@
       <c r="X442" s="15" t="n"/>
       <c r="Y442" s="15" t="n"/>
     </row>
-    <row r="443">
+    <row r="443" hidden="1" outlineLevel="1">
       <c r="A443" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30297,7 +30309,7 @@
       <c r="X443" s="15" t="n"/>
       <c r="Y443" s="15" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" hidden="1" outlineLevel="1">
       <c r="A444" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30362,7 +30374,7 @@
       <c r="X444" s="15" t="n"/>
       <c r="Y444" s="15" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" hidden="1" outlineLevel="1">
       <c r="A445" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30496,7 +30508,7 @@
       <c r="X446" s="15" t="n"/>
       <c r="Y446" s="15" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" hidden="1" outlineLevel="1">
       <c r="A447" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30565,7 +30577,7 @@
       <c r="X447" s="15" t="n"/>
       <c r="Y447" s="15" t="n"/>
     </row>
-    <row r="448">
+    <row r="448" hidden="1" outlineLevel="1">
       <c r="A448" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30699,7 +30711,7 @@
       <c r="X449" s="15" t="n"/>
       <c r="Y449" s="15" t="n"/>
     </row>
-    <row r="450">
+    <row r="450" hidden="1" outlineLevel="1">
       <c r="A450" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -30833,7 +30845,7 @@
       <c r="X451" s="15" t="n"/>
       <c r="Y451" s="15" t="n"/>
     </row>
-    <row r="452">
+    <row r="452" hidden="1" outlineLevel="1">
       <c r="A452" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31036,7 +31048,7 @@
       <c r="X454" s="15" t="n"/>
       <c r="Y454" s="15" t="n"/>
     </row>
-    <row r="455">
+    <row r="455" hidden="1" outlineLevel="1">
       <c r="A455" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31105,7 +31117,7 @@
       <c r="X455" s="15" t="n"/>
       <c r="Y455" s="15" t="n"/>
     </row>
-    <row r="456">
+    <row r="456" hidden="1" outlineLevel="1">
       <c r="A456" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31174,7 +31186,7 @@
       <c r="X456" s="15" t="n"/>
       <c r="Y456" s="15" t="n"/>
     </row>
-    <row r="457">
+    <row r="457" hidden="1" outlineLevel="1">
       <c r="A457" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31308,7 +31320,7 @@
       <c r="X458" s="15" t="n"/>
       <c r="Y458" s="15" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" hidden="1" outlineLevel="1">
       <c r="A459" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31373,7 +31385,7 @@
       <c r="X459" s="15" t="n"/>
       <c r="Y459" s="15" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" hidden="1" outlineLevel="1">
       <c r="A460" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31438,7 +31450,7 @@
       <c r="X460" s="15" t="n"/>
       <c r="Y460" s="15" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" hidden="1" outlineLevel="1">
       <c r="A461" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31568,7 +31580,7 @@
       <c r="X462" s="15" t="n"/>
       <c r="Y462" s="15" t="n"/>
     </row>
-    <row r="463">
+    <row r="463" hidden="1" outlineLevel="1">
       <c r="A463" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31633,7 +31645,7 @@
       <c r="X463" s="15" t="n"/>
       <c r="Y463" s="15" t="n"/>
     </row>
-    <row r="464">
+    <row r="464" hidden="1" outlineLevel="1">
       <c r="A464" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31763,7 +31775,7 @@
       <c r="X465" s="15" t="n"/>
       <c r="Y465" s="15" t="n"/>
     </row>
-    <row r="466">
+    <row r="466" hidden="1" outlineLevel="1">
       <c r="A466" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -31828,7 +31840,7 @@
       <c r="X466" s="15" t="n"/>
       <c r="Y466" s="15" t="n"/>
     </row>
-    <row r="467">
+    <row r="467" hidden="1" outlineLevel="1">
       <c r="A467" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32088,7 +32100,7 @@
       <c r="X470" s="15" t="n"/>
       <c r="Y470" s="15" t="n"/>
     </row>
-    <row r="471">
+    <row r="471" hidden="1" outlineLevel="1">
       <c r="A471" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32218,7 +32230,7 @@
       <c r="X472" s="15" t="n"/>
       <c r="Y472" s="15" t="n"/>
     </row>
-    <row r="473">
+    <row r="473" hidden="1" outlineLevel="1">
       <c r="A473" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32283,7 +32295,7 @@
       <c r="X473" s="15" t="n"/>
       <c r="Y473" s="15" t="n"/>
     </row>
-    <row r="474">
+    <row r="474" hidden="1" outlineLevel="1">
       <c r="A474" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32348,7 +32360,7 @@
       <c r="X474" s="15" t="n"/>
       <c r="Y474" s="15" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" hidden="1" outlineLevel="1">
       <c r="A475" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32543,7 +32555,7 @@
       <c r="X477" s="15" t="n"/>
       <c r="Y477" s="15" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" hidden="1" outlineLevel="1">
       <c r="A478" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32677,7 +32689,7 @@
       <c r="X479" s="15" t="n"/>
       <c r="Y479" s="15" t="n"/>
     </row>
-    <row r="480">
+    <row r="480" hidden="1" outlineLevel="1">
       <c r="A480" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32811,7 +32823,7 @@
       <c r="X481" s="15" t="n"/>
       <c r="Y481" s="15" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" hidden="1" outlineLevel="1">
       <c r="A482" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -32941,7 +32953,7 @@
       <c r="X483" s="15" t="n"/>
       <c r="Y483" s="15" t="n"/>
     </row>
-    <row r="484">
+    <row r="484" hidden="1" outlineLevel="1">
       <c r="A484" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33006,7 +33018,7 @@
       <c r="X484" s="15" t="n"/>
       <c r="Y484" s="15" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" hidden="1" outlineLevel="1">
       <c r="A485" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33071,7 +33083,7 @@
       <c r="X485" s="15" t="n"/>
       <c r="Y485" s="15" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" hidden="1" outlineLevel="1">
       <c r="A486" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33270,7 +33282,7 @@
       <c r="X488" s="15" t="n"/>
       <c r="Y488" s="15" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" hidden="1" outlineLevel="1">
       <c r="A489" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33339,7 +33351,7 @@
       <c r="X489" s="15" t="n"/>
       <c r="Y489" s="15" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" hidden="1" outlineLevel="1">
       <c r="A490" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33408,7 +33420,7 @@
       <c r="X490" s="15" t="n"/>
       <c r="Y490" s="15" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" hidden="1" outlineLevel="1">
       <c r="A491" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33542,7 +33554,7 @@
       <c r="X492" s="15" t="n"/>
       <c r="Y492" s="15" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" hidden="1" outlineLevel="1">
       <c r="A493" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33607,7 +33619,7 @@
       <c r="X493" s="15" t="n"/>
       <c r="Y493" s="15" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" hidden="1" outlineLevel="1">
       <c r="A494" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33737,7 +33749,7 @@
       <c r="X495" s="15" t="n"/>
       <c r="Y495" s="15" t="n"/>
     </row>
-    <row r="496">
+    <row r="496" hidden="1" outlineLevel="1">
       <c r="A496" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33867,7 +33879,7 @@
       <c r="X497" s="15" t="n"/>
       <c r="Y497" s="15" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" hidden="1" outlineLevel="1">
       <c r="A498" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -33932,7 +33944,7 @@
       <c r="X498" s="15" t="n"/>
       <c r="Y498" s="15" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" hidden="1" outlineLevel="1">
       <c r="A499" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34066,7 +34078,7 @@
       <c r="X500" s="15" t="n"/>
       <c r="Y500" s="15" t="n"/>
     </row>
-    <row r="501">
+    <row r="501" hidden="1" outlineLevel="1">
       <c r="A501" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34200,7 +34212,7 @@
       <c r="X502" s="15" t="n"/>
       <c r="Y502" s="15" t="n"/>
     </row>
-    <row r="503">
+    <row r="503" hidden="1" outlineLevel="1">
       <c r="A503" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34334,7 +34346,7 @@
       <c r="X504" s="15" t="n"/>
       <c r="Y504" s="15" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" hidden="1" outlineLevel="1">
       <c r="A505" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34533,7 +34545,7 @@
       <c r="X507" s="15" t="n"/>
       <c r="Y507" s="15" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" hidden="1" outlineLevel="1">
       <c r="A508" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34663,7 +34675,7 @@
       <c r="X509" s="15" t="n"/>
       <c r="Y509" s="15" t="n"/>
     </row>
-    <row r="510">
+    <row r="510" hidden="1" outlineLevel="1">
       <c r="A510" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34793,7 +34805,7 @@
       <c r="X511" s="15" t="n"/>
       <c r="Y511" s="15" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" hidden="1" outlineLevel="1">
       <c r="A512" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -34923,7 +34935,7 @@
       <c r="X513" s="15" t="n"/>
       <c r="Y513" s="15" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" hidden="1" outlineLevel="1">
       <c r="A514" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35053,7 +35065,7 @@
       <c r="X515" s="15" t="n"/>
       <c r="Y515" s="15" t="n"/>
     </row>
-    <row r="516">
+    <row r="516" hidden="1" outlineLevel="1">
       <c r="A516" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35183,7 +35195,7 @@
       <c r="X517" s="15" t="n"/>
       <c r="Y517" s="15" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" hidden="1" outlineLevel="1">
       <c r="A518" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35248,7 +35260,7 @@
       <c r="X518" s="15" t="n"/>
       <c r="Y518" s="15" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" hidden="1" outlineLevel="1">
       <c r="A519" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35378,7 +35390,7 @@
       <c r="X520" s="15" t="n"/>
       <c r="Y520" s="15" t="n"/>
     </row>
-    <row r="521">
+    <row r="521" hidden="1" outlineLevel="1">
       <c r="A521" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35508,7 +35520,7 @@
       <c r="X522" s="15" t="n"/>
       <c r="Y522" s="15" t="n"/>
     </row>
-    <row r="523">
+    <row r="523" hidden="1" outlineLevel="1">
       <c r="A523" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35573,7 +35585,7 @@
       <c r="X523" s="15" t="n"/>
       <c r="Y523" s="15" t="n"/>
     </row>
-    <row r="524">
+    <row r="524" hidden="1" outlineLevel="1">
       <c r="A524" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35638,7 +35650,7 @@
       <c r="X524" s="15" t="n"/>
       <c r="Y524" s="15" t="n"/>
     </row>
-    <row r="525">
+    <row r="525" hidden="1" outlineLevel="1">
       <c r="A525" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -35768,7 +35780,7 @@
       <c r="X526" s="15" t="n"/>
       <c r="Y526" s="15" t="n"/>
     </row>
-    <row r="527">
+    <row r="527" hidden="1" outlineLevel="1">
       <c r="A527" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36028,7 +36040,7 @@
       <c r="X530" s="15" t="n"/>
       <c r="Y530" s="15" t="n"/>
     </row>
-    <row r="531">
+    <row r="531" hidden="1" outlineLevel="1">
       <c r="A531" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36288,7 +36300,7 @@
       <c r="X534" s="15" t="n"/>
       <c r="Y534" s="15" t="n"/>
     </row>
-    <row r="535">
+    <row r="535" hidden="1" outlineLevel="1">
       <c r="A535" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36353,7 +36365,7 @@
       <c r="X535" s="15" t="n"/>
       <c r="Y535" s="15" t="n"/>
     </row>
-    <row r="536">
+    <row r="536" hidden="1" outlineLevel="1">
       <c r="A536" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36418,7 +36430,7 @@
       <c r="X536" s="15" t="n"/>
       <c r="Y536" s="15" t="n"/>
     </row>
-    <row r="537">
+    <row r="537" hidden="1" outlineLevel="1">
       <c r="A537" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36613,7 +36625,7 @@
       <c r="X539" s="15" t="n"/>
       <c r="Y539" s="15" t="n"/>
     </row>
-    <row r="540">
+    <row r="540" hidden="1" outlineLevel="1">
       <c r="A540" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36869,7 +36881,7 @@
       <c r="X543" s="15" t="n"/>
       <c r="Y543" s="15" t="n"/>
     </row>
-    <row r="544">
+    <row r="544" hidden="1" outlineLevel="1">
       <c r="A544" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -36934,7 +36946,7 @@
       <c r="X544" s="15" t="n"/>
       <c r="Y544" s="15" t="n"/>
     </row>
-    <row r="545">
+    <row r="545" hidden="1" outlineLevel="1">
       <c r="A545" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37064,7 +37076,7 @@
       <c r="X546" s="15" t="n"/>
       <c r="Y546" s="15" t="n"/>
     </row>
-    <row r="547">
+    <row r="547" hidden="1" outlineLevel="1">
       <c r="A547" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37129,7 +37141,7 @@
       <c r="X547" s="15" t="n"/>
       <c r="Y547" s="15" t="n"/>
     </row>
-    <row r="548">
+    <row r="548" hidden="1" outlineLevel="1">
       <c r="A548" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37259,7 +37271,7 @@
       <c r="X549" s="15" t="n"/>
       <c r="Y549" s="15" t="n"/>
     </row>
-    <row r="550">
+    <row r="550" hidden="1" outlineLevel="1">
       <c r="A550" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37324,7 +37336,7 @@
       <c r="X550" s="15" t="n"/>
       <c r="Y550" s="15" t="n"/>
     </row>
-    <row r="551">
+    <row r="551" hidden="1" outlineLevel="1">
       <c r="A551" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37450,7 +37462,7 @@
       <c r="X552" s="15" t="n"/>
       <c r="Y552" s="15" t="n"/>
     </row>
-    <row r="553">
+    <row r="553" hidden="1" outlineLevel="1">
       <c r="A553" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37576,7 +37588,7 @@
       <c r="X554" s="15" t="n"/>
       <c r="Y554" s="15" t="n"/>
     </row>
-    <row r="555">
+    <row r="555" hidden="1" outlineLevel="1">
       <c r="A555" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37641,7 +37653,7 @@
       <c r="X555" s="15" t="n"/>
       <c r="Y555" s="15" t="n"/>
     </row>
-    <row r="556">
+    <row r="556" hidden="1" outlineLevel="1">
       <c r="A556" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -37970,7 +37982,7 @@
       <c r="X560" s="15" t="n"/>
       <c r="Y560" s="15" t="n"/>
     </row>
-    <row r="561">
+    <row r="561" hidden="1" outlineLevel="1">
       <c r="A561" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38035,7 +38047,7 @@
       <c r="X561" s="15" t="n"/>
       <c r="Y561" s="15" t="n"/>
     </row>
-    <row r="562">
+    <row r="562" hidden="1" outlineLevel="1">
       <c r="A562" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38100,7 +38112,7 @@
       <c r="X562" s="15" t="n"/>
       <c r="Y562" s="15" t="n"/>
     </row>
-    <row r="563">
+    <row r="563" hidden="1" outlineLevel="1">
       <c r="A563" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38295,7 +38307,7 @@
       <c r="X565" s="15" t="n"/>
       <c r="Y565" s="15" t="n"/>
     </row>
-    <row r="566">
+    <row r="566" hidden="1" outlineLevel="1">
       <c r="A566" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38360,7 +38372,7 @@
       <c r="X566" s="15" t="n"/>
       <c r="Y566" s="15" t="n"/>
     </row>
-    <row r="567">
+    <row r="567" hidden="1" outlineLevel="1">
       <c r="A567" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38490,7 +38502,7 @@
       <c r="X568" s="15" t="n"/>
       <c r="Y568" s="15" t="n"/>
     </row>
-    <row r="569">
+    <row r="569" hidden="1" outlineLevel="1">
       <c r="A569" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38555,7 +38567,7 @@
       <c r="X569" s="15" t="n"/>
       <c r="Y569" s="15" t="n"/>
     </row>
-    <row r="570">
+    <row r="570" hidden="1" outlineLevel="1">
       <c r="A570" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38685,7 +38697,7 @@
       <c r="X571" s="15" t="n"/>
       <c r="Y571" s="15" t="n"/>
     </row>
-    <row r="572">
+    <row r="572" hidden="1" outlineLevel="1">
       <c r="A572" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38750,7 +38762,7 @@
       <c r="X572" s="15" t="n"/>
       <c r="Y572" s="15" t="n"/>
     </row>
-    <row r="573">
+    <row r="573" hidden="1" outlineLevel="1">
       <c r="A573" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38815,7 +38827,7 @@
       <c r="X573" s="15" t="n"/>
       <c r="Y573" s="15" t="n"/>
     </row>
-    <row r="574">
+    <row r="574" hidden="1" outlineLevel="1">
       <c r="A574" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -38880,7 +38892,7 @@
       <c r="X574" s="15" t="n"/>
       <c r="Y574" s="15" t="n"/>
     </row>
-    <row r="575">
+    <row r="575" hidden="1" outlineLevel="1">
       <c r="A575" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39010,7 +39022,7 @@
       <c r="X576" s="15" t="n"/>
       <c r="Y576" s="15" t="n"/>
     </row>
-    <row r="577">
+    <row r="577" hidden="1" outlineLevel="1">
       <c r="A577" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39075,7 +39087,7 @@
       <c r="X577" s="15" t="n"/>
       <c r="Y577" s="15" t="n"/>
     </row>
-    <row r="578">
+    <row r="578" hidden="1" outlineLevel="1">
       <c r="A578" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39140,7 +39152,7 @@
       <c r="X578" s="15" t="n"/>
       <c r="Y578" s="15" t="n"/>
     </row>
-    <row r="579">
+    <row r="579" hidden="1" outlineLevel="1">
       <c r="A579" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39270,7 +39282,7 @@
       <c r="X580" s="15" t="n"/>
       <c r="Y580" s="15" t="n"/>
     </row>
-    <row r="581">
+    <row r="581" hidden="1" outlineLevel="1">
       <c r="A581" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39335,7 +39347,7 @@
       <c r="X581" s="15" t="n"/>
       <c r="Y581" s="15" t="n"/>
     </row>
-    <row r="582">
+    <row r="582" hidden="1" outlineLevel="1">
       <c r="A582" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39530,7 +39542,7 @@
       <c r="X584" s="15" t="n"/>
       <c r="Y584" s="15" t="n"/>
     </row>
-    <row r="585">
+    <row r="585" hidden="1" outlineLevel="1">
       <c r="A585" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39595,7 +39607,7 @@
       <c r="X585" s="15" t="n"/>
       <c r="Y585" s="15" t="n"/>
     </row>
-    <row r="586">
+    <row r="586" hidden="1" outlineLevel="1">
       <c r="A586" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39725,7 +39737,7 @@
       <c r="X587" s="15" t="n"/>
       <c r="Y587" s="15" t="n"/>
     </row>
-    <row r="588">
+    <row r="588" hidden="1" outlineLevel="1">
       <c r="A588" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39855,7 +39867,7 @@
       <c r="X589" s="15" t="n"/>
       <c r="Y589" s="15" t="n"/>
     </row>
-    <row r="590">
+    <row r="590" hidden="1" outlineLevel="1">
       <c r="A590" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39920,7 +39932,7 @@
       <c r="X590" s="15" t="n"/>
       <c r="Y590" s="15" t="n"/>
     </row>
-    <row r="591">
+    <row r="591" hidden="1" outlineLevel="1">
       <c r="A591" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -39985,7 +39997,7 @@
       <c r="X591" s="15" t="n"/>
       <c r="Y591" s="15" t="n"/>
     </row>
-    <row r="592">
+    <row r="592" hidden="1" outlineLevel="1">
       <c r="A592" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40050,7 +40062,7 @@
       <c r="X592" s="15" t="n"/>
       <c r="Y592" s="15" t="n"/>
     </row>
-    <row r="593">
+    <row r="593" hidden="1" outlineLevel="1">
       <c r="A593" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40180,7 +40192,7 @@
       <c r="X594" s="15" t="n"/>
       <c r="Y594" s="15" t="n"/>
     </row>
-    <row r="595">
+    <row r="595" hidden="1" outlineLevel="1">
       <c r="A595" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40367,7 +40379,7 @@
       <c r="X597" s="15" t="n"/>
       <c r="Y597" s="15" t="n"/>
     </row>
-    <row r="598">
+    <row r="598" hidden="1" outlineLevel="1">
       <c r="A598" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40558,7 +40570,7 @@
       <c r="X600" s="15" t="n"/>
       <c r="Y600" s="15" t="n"/>
     </row>
-    <row r="601">
+    <row r="601" hidden="1" outlineLevel="1">
       <c r="A601" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40688,7 +40700,7 @@
       <c r="X602" s="15" t="n"/>
       <c r="Y602" s="15" t="n"/>
     </row>
-    <row r="603">
+    <row r="603" hidden="1" outlineLevel="1">
       <c r="A603" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40818,7 +40830,7 @@
       <c r="X604" s="15" t="n"/>
       <c r="Y604" s="15" t="n"/>
     </row>
-    <row r="605">
+    <row r="605" hidden="1" outlineLevel="1">
       <c r="A605" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -40883,7 +40895,7 @@
       <c r="X605" s="15" t="n"/>
       <c r="Y605" s="15" t="n"/>
     </row>
-    <row r="606">
+    <row r="606" hidden="1" outlineLevel="1">
       <c r="A606" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41017,7 +41029,7 @@
       <c r="X607" s="15" t="n"/>
       <c r="Y607" s="15" t="n"/>
     </row>
-    <row r="608">
+    <row r="608" hidden="1" outlineLevel="1">
       <c r="A608" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41086,7 +41098,7 @@
       <c r="X608" s="15" t="n"/>
       <c r="Y608" s="15" t="n"/>
     </row>
-    <row r="609">
+    <row r="609" hidden="1" outlineLevel="1">
       <c r="A609" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41220,7 +41232,7 @@
       <c r="X610" s="15" t="n"/>
       <c r="Y610" s="15" t="n"/>
     </row>
-    <row r="611">
+    <row r="611" hidden="1" outlineLevel="1">
       <c r="A611" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41350,7 +41362,7 @@
       <c r="X612" s="15" t="n"/>
       <c r="Y612" s="15" t="n"/>
     </row>
-    <row r="613">
+    <row r="613" hidden="1" outlineLevel="1">
       <c r="A613" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41415,7 +41427,7 @@
       <c r="X613" s="15" t="n"/>
       <c r="Y613" s="15" t="n"/>
     </row>
-    <row r="614">
+    <row r="614" hidden="1" outlineLevel="1">
       <c r="A614" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41545,7 +41557,7 @@
       <c r="X615" s="15" t="n"/>
       <c r="Y615" s="15" t="n"/>
     </row>
-    <row r="616">
+    <row r="616" hidden="1" outlineLevel="1">
       <c r="A616" s="10" t="inlineStr">
         <is>
           <t>P3</t>
@@ -41740,7 +41752,7 @@
       <c r="X618" s="15" t="n"/>
       <c r="Y618" s="15" t="n"/>
     </row>
-    <row r="619">
+    <row r="619" hidden="1" outlineLevel="1">
       <c r="A619" s="10" t="inlineStr">
         <is>
           <t>P3</t>

--- a/blanketter/blankett_forvaltarkunskap_nnk.xlsx
+++ b/blanketter/blankett_forvaltarkunskap_nnk.xlsx
@@ -741,7 +741,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.7, 2026-08-27</t>
+          <t>Länsstyrelsen i Södermanlands län · Naturskyddsenheten · NNK/NRF ref. 2451-2026 · version 1.8, 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="84" customHeight="1">
+    <row r="18" ht="112" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>9.</t>
@@ -877,7 +877,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kolumn K, "Uppföljningsplan (LST, intern)", är nytt sedan version 1.4 — automatiskt hämtat ur länsstyrelsens interna uppföljningsplaner (153 av 628 rader har en träff, 38 objekt totalt). Visar en målindikator för naturtypen (t.ex. "Död ved", "Granens andel av trädskiktet") med länk till källdokumentet på G:. Källan kallas "Bevarandeplaner" i mappstrukturen på G: men innehåller uppföljningsplaner, inte bevarandetillstånd — förväxla inte med kolumn J. Ett stöd inför Vad ska kontrolleras och Metod för kontroll — inget facit.</t>
+          <t>Kolumn K, "Uppföljningsplan (LST, intern)", är nytt sedan version 1.4 — automatiskt hämtat ur länsstyrelsens interna uppföljningsplaner (153 av 628 rader har en träff, 38 objekt totalt). Visar en målindikator för naturtypen (t.ex. "Död ved", "Granens andel av trädskiktet") med länk till källdokumentet på G:. Källan kallas "Bevarandeplaner" i mappstrukturen på G: men innehåller uppföljningsplaner, inte bevarandetillstånd — förväxla inte med kolumn J. Ett stöd inför Vad ska kontrolleras och Metod för kontroll — inget facit. Sedan version 1.8 avslutas texten med dokumentets årtal inom parentes, t.ex. "...(2018)" — samtliga 38 uppföljningsplaner är från 2017 eller 2018, alltså 8–9 år gamla. Fråga alltid förvaltaren om det stämmer fortfarande (se regel R3).</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till)</t>
+          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L48" s="14" t="n"/>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070, 2180)</t>
+          <t>Död ved (9010, 9070, 2180) (2017)</t>
         </is>
       </c>
       <c r="L49" s="14" t="n"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L50" s="14" t="n"/>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+3 till) (2017)</t>
         </is>
       </c>
       <c r="L51" s="14" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L52" s="14" t="n"/>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (1630, 6270, 6510)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (1630, 6270, 6510) (2017)</t>
         </is>
       </c>
       <c r="L53" s="14" t="n"/>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+3 till) (2017)</t>
         </is>
       </c>
       <c r="L54" s="14" t="n"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070, 2180)</t>
+          <t>Död ved (9010, 9070, 2180) (2017)</t>
         </is>
       </c>
       <c r="L55" s="14" t="n"/>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L56" s="14" t="n"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L57" s="14" t="n"/>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L58" s="14" t="n"/>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070, 2180)</t>
+          <t>Död ved (9010, 9070, 2180) (2017)</t>
         </is>
       </c>
       <c r="L59" s="14" t="n"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L60" s="14" t="n"/>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L61" s="14" t="n"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L103" s="14" t="n"/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L104" s="14" t="n"/>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="K105" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L105" s="14" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L106" s="14" t="n"/>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (5130, 6270, 64... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L107" s="14" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (3 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (3 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L108" s="14" t="n"/>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070)</t>
+          <t>Död ved (9010, 9070) (2018)</t>
         </is>
       </c>
       <c r="L109" s="14" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till)</t>
+          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L110" s="14" t="n"/>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="K111" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L111" s="14" t="n"/>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L112" s="14" t="n"/>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="K113" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L113" s="14" t="n"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L114" s="14" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="K115" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L115" s="14" t="n"/>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L116" s="14" t="n"/>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070)</t>
+          <t>Död ved (9010, 9070) (2018)</t>
         </is>
       </c>
       <c r="L117" s="14" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6510) (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L118" s="14" t="n"/>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="K119" s="12" t="inlineStr">
         <is>
-          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till)</t>
+          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (6270, 6510, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L119" s="14" t="n"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L120" s="14" t="n"/>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="K121" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L121" s="14" t="n"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9070)</t>
+          <t>Död ved (9010, 9070) (2018)</t>
         </is>
       </c>
       <c r="L128" s="14" t="n"/>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="K129" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L129" s="14" t="n"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (1620, 1630, 6270, 8230, 9070)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (1620, 1630, 6270, 8230, 9070) (2018)</t>
         </is>
       </c>
       <c r="L130" s="14" t="n"/>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L131" s="14" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L132" s="14" t="n"/>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6270, 82... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L133" s="14" t="n"/>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L134" s="14" t="n"/>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="K135" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L135" s="14" t="n"/>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L136" s="14" t="n"/>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L141" s="14" t="n"/>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>Det ska finna tillräckligt inslag av död ved (9010, 9050)</t>
+          <t>Det ska finna tillräckligt inslag av död ved (9010, 9050) (2017)</t>
         </is>
       </c>
       <c r="L142" s="14" t="n"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="K143" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L143" s="14" t="n"/>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070)</t>
+          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070) (2017)</t>
         </is>
       </c>
       <c r="L144" s="14" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070)</t>
+          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070) (2017)</t>
         </is>
       </c>
       <c r="L145" s="14" t="n"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L146" s="14" t="n"/>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070)</t>
+          <t>Inslaget av igenväxningsvegetation ska vara mycket begränsat (9070) (2017)</t>
         </is>
       </c>
       <c r="L147" s="14" t="n"/>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (8 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L148" s="14" t="n"/>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="K160" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L160" s="14" t="n"/>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="K161" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L161" s="14" t="n"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="K162" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L162" s="14" t="n"/>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="K163" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L163" s="14" t="n"/>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="K164" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L164" s="14" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="K165" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L165" s="14" t="n"/>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="K166" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6410, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L166" s="14" t="n"/>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="K184" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L184" s="14" t="n"/>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="K185" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L185" s="14" t="n"/>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="K186" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L186" s="14" t="n"/>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="K187" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L187" s="14" t="n"/>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="K188" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (1630, 6230, 62... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L188" s="14" t="n"/>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="K199" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L199" s="14" t="n"/>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="K200" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2018)</t>
         </is>
       </c>
       <c r="L200" s="14" t="n"/>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="K201" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2018)</t>
         </is>
       </c>
       <c r="L201" s="14" t="n"/>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="K202" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L202" s="14" t="n"/>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="K203" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L203" s="14" t="n"/>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="K227" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6280) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6280) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L227" s="14" t="n"/>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="K228" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd samt även idegran för...</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd samt även idegran för... (2018)</t>
         </is>
       </c>
       <c r="L228" s="14" t="n"/>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="K244" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9080)</t>
+          <t>Död ved (9010, 9080) (2018)</t>
         </is>
       </c>
       <c r="L244" s="14" t="n"/>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="K245" s="12" t="inlineStr">
         <is>
-          <t>Negativa indikatorarter (7230)</t>
+          <t>Negativa indikatorarter (7230) (2018)</t>
         </is>
       </c>
       <c r="L245" s="14" t="n"/>
@@ -17342,7 +17342,7 @@
       </c>
       <c r="K246" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i lövs... (+1 till)</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i lövs... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L246" s="14" t="n"/>
@@ -17411,7 +17411,7 @@
       </c>
       <c r="K247" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut (1630) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut (1630) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L247" s="14" t="n"/>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="K265" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L265" s="14" t="n"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="K266" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut (9070) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut (9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L266" s="14" t="n"/>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="K267" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L267" s="14" t="n"/>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="K268" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L268" s="14" t="n"/>
@@ -18837,7 +18837,7 @@
       </c>
       <c r="K269" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L269" s="14" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="K270" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L270" s="14" t="n"/>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="K273" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L273" s="14" t="n"/>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="K274" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L274" s="14" t="n"/>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="K275" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (5 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L275" s="14" t="n"/>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="K276" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2017)</t>
         </is>
       </c>
       <c r="L276" s="14" t="n"/>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="K277" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2017)</t>
         </is>
       </c>
       <c r="L277" s="14" t="n"/>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="K278" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2018)</t>
         </is>
       </c>
       <c r="L278" s="14" t="n"/>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="K279" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L279" s="14" t="n"/>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="K280" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i eksk... (2018)</t>
         </is>
       </c>
       <c r="L280" s="14" t="n"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="K305" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall och triviallövträd för att bestånden ska ... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall och triviallövträd för att bestånden ska ... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L305" s="14" t="n"/>
@@ -21286,7 +21286,7 @@
       </c>
       <c r="K306" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L306" s="14" t="n"/>
@@ -21355,7 +21355,7 @@
       </c>
       <c r="K307" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L307" s="14" t="n"/>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="K308" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i taig...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i taig... (2018)</t>
         </is>
       </c>
       <c r="L308" s="14" t="n"/>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="K309" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L309" s="14" t="n"/>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="K317" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska vara begränsat så att död ved och grova tallar ska vara fortsatt s... (+1 till)</t>
+          <t>Inslaget av gran ska vara begränsat så att död ved och grova tallar ska vara fortsatt s... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L317" s="14" t="n"/>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="K318" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (9 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (9 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L318" s="14" t="n"/>
@@ -22155,7 +22155,7 @@
       </c>
       <c r="K319" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (9 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (9 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L319" s="14" t="n"/>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="K334" s="12" t="inlineStr">
         <is>
-          <t>Brandsubstrat för brandgynnade arter. (9010) (+1 till)</t>
+          <t>Brandsubstrat för brandgynnade arter. (9010) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L334" s="14" t="n"/>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="K335" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L335" s="14" t="n"/>
@@ -23532,7 +23532,7 @@
       </c>
       <c r="K340" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att långsiktigt b... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L340" s="14" t="n"/>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="K341" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L341" s="14" t="n"/>
@@ -23670,7 +23670,7 @@
       </c>
       <c r="K342" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2018)</t>
         </is>
       </c>
       <c r="L342" s="14" t="n"/>
@@ -24507,7 +24507,7 @@
       </c>
       <c r="K355" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall och triviallövträd för att långsiktigt bi... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall och triviallövträd för att långsiktigt bi... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L355" s="14" t="n"/>
@@ -25799,7 +25799,7 @@
       </c>
       <c r="K375" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (3 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (3 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L375" s="14" t="n"/>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="K376" s="12" t="inlineStr">
         <is>
-          <t>Vidkroniga grova träd som tidigare stått ljusöppet ska stå fria i kronan (9160)</t>
+          <t>Vidkroniga grova träd som tidigare stått ljusöppet ska stå fria i kronan (9160) (2017)</t>
         </is>
       </c>
       <c r="L376" s="14" t="n"/>
@@ -26197,7 +26197,7 @@
       </c>
       <c r="K381" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall- och triviallövträd för att bestånden ska... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L381" s="14" t="n"/>
@@ -26266,7 +26266,7 @@
       </c>
       <c r="K382" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i lövs...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i lövs... (2017)</t>
         </is>
       </c>
       <c r="L382" s="14" t="n"/>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="K383" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L383" s="14" t="n"/>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="K384" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (6 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L384" s="14" t="n"/>
@@ -26668,7 +26668,7 @@
       </c>
       <c r="K388" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L388" s="14" t="n"/>
@@ -26737,7 +26737,7 @@
       </c>
       <c r="K389" s="12" t="inlineStr">
         <is>
-          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i taig...</t>
+          <t>Inslaget av gran ska inte påverka artsammansättning eller konkurrensförhållanden i taig... (2017)</t>
         </is>
       </c>
       <c r="L389" s="14" t="n"/>
@@ -26806,7 +26806,7 @@
       </c>
       <c r="K390" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L390" s="14" t="n"/>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="K393" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+3 till) (2017)</t>
         </is>
       </c>
       <c r="L393" s="14" t="n"/>
@@ -27074,7 +27074,7 @@
       </c>
       <c r="K394" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+3 till) (2017)</t>
         </is>
       </c>
       <c r="L394" s="14" t="n"/>
@@ -27143,7 +27143,7 @@
       </c>
       <c r="K395" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9020, 9070)</t>
+          <t>Död ved (9020, 9070) (2017)</t>
         </is>
       </c>
       <c r="L395" s="14" t="n"/>
@@ -27212,7 +27212,7 @@
       </c>
       <c r="K396" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 6410, 8230, 9070)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 6410, 8230, 9070) (2017)</t>
         </is>
       </c>
       <c r="L396" s="14" t="n"/>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="K397" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410, 9070) (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L397" s="14" t="n"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K398" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till) (2018)</t>
         </is>
       </c>
       <c r="L398" s="14" t="n"/>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="K399" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till) (2018)</t>
         </is>
       </c>
       <c r="L399" s="14" t="n"/>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="K400" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+3 till) (2018)</t>
         </is>
       </c>
       <c r="L400" s="14" t="n"/>
@@ -28987,7 +28987,7 @@
       </c>
       <c r="K423" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (9070) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L423" s="14" t="n"/>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="K424" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (8230, 9070)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (8230, 9070) (2018)</t>
         </is>
       </c>
       <c r="L424" s="14" t="n"/>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="K436" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L436" s="14" t="n"/>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="K437" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L437" s="14" t="n"/>
@@ -29978,7 +29978,7 @@
       </c>
       <c r="K438" s="12" t="inlineStr">
         <is>
-          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (silikatgräsmark ...</t>
+          <t>Rödlistade ängs- och hagmarksväxter ska finnas i livskraftiga bestånd (silikatgräsmark ... (2017)</t>
         </is>
       </c>
       <c r="L438" s="14" t="n"/>
@@ -30502,7 +30502,7 @@
       </c>
       <c r="K446" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L446" s="14" t="n"/>
@@ -30571,7 +30571,7 @@
       </c>
       <c r="K447" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L447" s="14" t="n"/>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="K448" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6230, 6270, 6410) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L448" s="14" t="n"/>
@@ -30839,7 +30839,7 @@
       </c>
       <c r="K451" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410) (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410) (+2 till) (2017)</t>
         </is>
       </c>
       <c r="L451" s="14" t="n"/>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="K452" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410) (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (6270, 6410) (+2 till) (2017)</t>
         </is>
       </c>
       <c r="L452" s="14" t="n"/>
@@ -31042,7 +31042,7 @@
       </c>
       <c r="K454" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L454" s="14" t="n"/>
@@ -31111,7 +31111,7 @@
       </c>
       <c r="K455" s="12" t="inlineStr">
         <is>
-          <t>Död ved i olika stadier av nedbrytning och former, såsom lågor, torrakor, högstubbar, h...</t>
+          <t>Död ved i olika stadier av nedbrytning och former, såsom lågor, torrakor, högstubbar, h... (2018)</t>
         </is>
       </c>
       <c r="L455" s="14" t="n"/>
@@ -31180,7 +31180,7 @@
       </c>
       <c r="K456" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd och/eller triviallövträd för att l... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L456" s="14" t="n"/>
@@ -31249,7 +31249,7 @@
       </c>
       <c r="K457" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (6270, 9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L457" s="14" t="n"/>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="K470" s="12" t="inlineStr">
         <is>
-          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (9070) (+1 till)</t>
+          <t>Förekomst av igenväxningsvegetation ska vara mkt begränsad (9070) (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L470" s="14" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="K471" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädellövträd för att långsiktigt bibehålla dess... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädellövträd för att långsiktigt bibehålla dess... (+1 till) (2018)</t>
         </is>
       </c>
       <c r="L471" s="14" t="n"/>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="K479" s="12" t="inlineStr">
         <is>
-          <t>Gran ska inte konkurrera ut lövträd, tall eller naturvårdsträd. (9070) (+2 till)</t>
+          <t>Gran ska inte konkurrera ut lövträd, tall eller naturvårdsträd. (9070) (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L479" s="14" t="n"/>
@@ -32752,7 +32752,7 @@
       </c>
       <c r="K480" s="12" t="inlineStr">
         <is>
-          <t>Igenväxningsvegetation ska inte konkurrera ut typiska arter i området. (6110, 9070) (+2 till)</t>
+          <t>Igenväxningsvegetation ska inte konkurrera ut typiska arter i området. (6110, 9070) (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L480" s="14" t="n"/>
@@ -33276,7 +33276,7 @@
       </c>
       <c r="K488" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+2 till) (2017)</t>
         </is>
       </c>
       <c r="L488" s="14" t="n"/>
@@ -33345,7 +33345,7 @@
       </c>
       <c r="K489" s="12" t="inlineStr">
         <is>
-          <t>Död ved (9010, 9050, 9080)</t>
+          <t>Död ved (9010, 9050, 9080) (2017)</t>
         </is>
       </c>
       <c r="L489" s="14" t="n"/>
@@ -33414,7 +33414,7 @@
       </c>
       <c r="K490" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av ädel- och triviallövträd för att bestånden ska... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L490" s="14" t="n"/>
@@ -33483,7 +33483,7 @@
       </c>
       <c r="K491" s="12" t="inlineStr">
         <is>
-          <t>Igenväxning av öppna myrhabitat (7230) (+1 till)</t>
+          <t>Igenväxning av öppna myrhabitat (7230) (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L491" s="14" t="n"/>
@@ -34072,7 +34072,7 @@
       </c>
       <c r="K500" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L500" s="14" t="n"/>
@@ -34141,7 +34141,7 @@
       </c>
       <c r="K501" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (4 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L501" s="14" t="n"/>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="K504" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall och ädellövträd för att långsiktigt bibeh... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall och ädellövträd för att långsiktigt bibeh... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L504" s="14" t="n"/>
@@ -34409,7 +34409,7 @@
       </c>
       <c r="K505" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av tall och ädellövträd för att långsiktigt bibeh... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av tall och ädellövträd för att långsiktigt bibeh... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L505" s="14" t="n"/>
@@ -35514,7 +35514,7 @@
       </c>
       <c r="K522" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L522" s="14" t="n"/>
@@ -35579,7 +35579,7 @@
       </c>
       <c r="K523" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L523" s="14" t="n"/>
@@ -35644,7 +35644,7 @@
       </c>
       <c r="K524" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L524" s="14" t="n"/>
@@ -35709,7 +35709,7 @@
       </c>
       <c r="K525" s="12" t="inlineStr">
         <is>
-          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod)</t>
+          <t>Uppföljningsplan finns för objektet (2 indikatorer, ej för denna kod) (2017)</t>
         </is>
       </c>
       <c r="L525" s="14" t="n"/>
@@ -37781,7 +37781,7 @@
       </c>
       <c r="K557" s="12" t="inlineStr">
         <is>
-          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (kalkgräsmark (... (+2 till)</t>
+          <t>Grässvålen ska vara väl avbetad/avslagen vid vegetationsperiodens slut. (kalkgräsmark (... (+2 till) (2017)</t>
         </is>
       </c>
       <c r="L557" s="14" t="n"/>
@@ -41023,7 +41023,7 @@
       </c>
       <c r="K607" s="12" t="inlineStr">
         <is>
-          <t>Död ved i olika stadier av nedbrytning och former, såsom lågor, torrakor, högstubbar oc...</t>
+          <t>Död ved i olika stadier av nedbrytning och former, såsom lågor, torrakor, högstubbar oc... (2018)</t>
         </is>
       </c>
       <c r="L607" s="14" t="n"/>
@@ -41092,7 +41092,7 @@
       </c>
       <c r="K608" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av lövträd och/eller tall i områden där dessa trä... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av lövträd och/eller tall i områden där dessa trä... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L608" s="14" t="n"/>
@@ -41161,7 +41161,7 @@
       </c>
       <c r="K609" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av lövträd och/eller tall i områden där dessa trä... (+2 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av lövträd och/eller tall i områden där dessa trä... (+2 till) (2018)</t>
         </is>
       </c>
       <c r="L609" s="14" t="n"/>
@@ -42396,7 +42396,7 @@
       </c>
       <c r="K628" s="12" t="inlineStr">
         <is>
-          <t>Det ska finnas tillräcklig föryngring av triviallövträd för att bestånden ska bestå gen... (+1 till)</t>
+          <t>Det ska finnas tillräcklig föryngring av triviallövträd för att bestånden ska bestå gen... (+1 till) (2017)</t>
         </is>
       </c>
       <c r="L628" s="14" t="n"/>
